--- a/output/VFL_2026_Stage1_W1_Report.xlsx
+++ b/output/VFL_2026_Stage1_W1_Report.xlsx
@@ -64,12 +64,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
+        <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
+        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
     <fill>
@@ -96,9 +96,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -466,7 +466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -478,6 +478,8 @@
     <col width="15" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
     <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -518,10 +520,20 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>Actual Pts</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Diff</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>With IGL</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>IGL?</t>
         </is>
@@ -560,9 +572,15 @@
         <v>12.5</v>
       </c>
       <c r="H2" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="J2" s="2" t="n">
         <v>25</v>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>IGL</t>
         </is>
@@ -601,9 +619,15 @@
         <v>11.3</v>
       </c>
       <c r="H3" t="n">
+        <v>11</v>
+      </c>
+      <c r="I3" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="J3" t="n">
         <v>11.3</v>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -638,9 +662,15 @@
         <v>9.5</v>
       </c>
       <c r="H4" t="n">
+        <v>7</v>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="J4" t="n">
         <v>9.5</v>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -675,9 +705,15 @@
         <v>8.6</v>
       </c>
       <c r="H5" t="n">
+        <v>5</v>
+      </c>
+      <c r="I5" s="3" t="n">
+        <v>-3.6</v>
+      </c>
+      <c r="J5" t="n">
         <v>8.6</v>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -712,9 +748,15 @@
         <v>10.1</v>
       </c>
       <c r="H6" t="n">
+        <v>6</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>-4.1</v>
+      </c>
+      <c r="J6" t="n">
         <v>10.1</v>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -749,9 +791,15 @@
         <v>8.300000000000001</v>
       </c>
       <c r="H7" t="n">
+        <v>6</v>
+      </c>
+      <c r="I7" s="3" t="n">
+        <v>-2.3</v>
+      </c>
+      <c r="J7" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -786,9 +834,15 @@
         <v>7.9</v>
       </c>
       <c r="H8" t="n">
+        <v>10</v>
+      </c>
+      <c r="I8" s="4" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J8" t="n">
         <v>7.9</v>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -823,9 +877,15 @@
         <v>7.5</v>
       </c>
       <c r="H9" t="n">
+        <v>2</v>
+      </c>
+      <c r="I9" s="3" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="J9" t="n">
         <v>7.5</v>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -860,9 +920,15 @@
         <v>12.3</v>
       </c>
       <c r="H10" t="n">
+        <v>8</v>
+      </c>
+      <c r="I10" s="3" t="n">
+        <v>-4.3</v>
+      </c>
+      <c r="J10" t="n">
         <v>12.3</v>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -897,9 +963,15 @@
         <v>8.199999999999999</v>
       </c>
       <c r="H11" t="n">
+        <v>6</v>
+      </c>
+      <c r="I11" s="3" t="n">
+        <v>-2.2</v>
+      </c>
+      <c r="J11" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -934,12 +1006,18 @@
         <v>7.4</v>
       </c>
       <c r="H12" t="n">
+        <v>7</v>
+      </c>
+      <c r="I12" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="J12" t="n">
         <v>7.4</v>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
@@ -948,6 +1026,9 @@
         <v>100</v>
       </c>
       <c r="H14" t="n">
+        <v>75</v>
+      </c>
+      <c r="J14" t="n">
         <v>116.2</v>
       </c>
     </row>
@@ -962,7 +1043,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -974,6 +1055,8 @@
     <col width="15" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
     <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1014,10 +1097,20 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>Actual Pts</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Diff</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>With IGL</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>IGL?</t>
         </is>
@@ -1056,9 +1149,15 @@
         <v>7.6</v>
       </c>
       <c r="H2" t="n">
+        <v>10</v>
+      </c>
+      <c r="I2" s="4" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="J2" t="n">
         <v>7.6</v>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1093,9 +1192,15 @@
         <v>11.4</v>
       </c>
       <c r="H3" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>-6.4</v>
+      </c>
+      <c r="J3" s="2" t="n">
         <v>22.9</v>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>IGL</t>
         </is>
@@ -1134,9 +1239,15 @@
         <v>8</v>
       </c>
       <c r="H4" t="n">
+        <v>5</v>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>-3</v>
+      </c>
+      <c r="J4" t="n">
         <v>8</v>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1171,9 +1282,15 @@
         <v>8.4</v>
       </c>
       <c r="H5" t="n">
+        <v>9</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J5" t="n">
         <v>8.4</v>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1208,9 +1325,15 @@
         <v>9.4</v>
       </c>
       <c r="H6" t="n">
+        <v>14</v>
+      </c>
+      <c r="I6" s="4" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J6" t="n">
         <v>9.4</v>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1245,9 +1368,15 @@
         <v>7.7</v>
       </c>
       <c r="H7" t="n">
+        <v>8</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="J7" t="n">
         <v>7.7</v>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1282,9 +1411,15 @@
         <v>7.9</v>
       </c>
       <c r="H8" t="n">
+        <v>10</v>
+      </c>
+      <c r="I8" s="4" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J8" t="n">
         <v>7.9</v>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1319,9 +1454,15 @@
         <v>6.9</v>
       </c>
       <c r="H9" t="n">
+        <v>10</v>
+      </c>
+      <c r="I9" s="4" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J9" t="n">
         <v>6.9</v>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1356,9 +1497,15 @@
         <v>10.7</v>
       </c>
       <c r="H10" t="n">
+        <v>15</v>
+      </c>
+      <c r="I10" s="4" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J10" t="n">
         <v>10.7</v>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1393,9 +1540,15 @@
         <v>9</v>
       </c>
       <c r="H11" t="n">
+        <v>4</v>
+      </c>
+      <c r="I11" s="3" t="n">
+        <v>-5</v>
+      </c>
+      <c r="J11" t="n">
         <v>9</v>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1430,12 +1583,18 @@
         <v>7.4</v>
       </c>
       <c r="H12" t="n">
+        <v>8</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J12" t="n">
         <v>7.4</v>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
@@ -1444,6 +1603,9 @@
         <v>100</v>
       </c>
       <c r="H14" t="n">
+        <v>98</v>
+      </c>
+      <c r="J14" t="n">
         <v>105.9</v>
       </c>
     </row>
@@ -3269,7 +3431,7 @@
       <c r="G39" t="n">
         <v>12.3</v>
       </c>
-      <c r="H39" s="5" t="n">
+      <c r="H39" s="3" t="n">
         <v>-4.3</v>
       </c>
       <c r="I39" t="n">
@@ -3315,7 +3477,7 @@
       <c r="G40" t="n">
         <v>10.4</v>
       </c>
-      <c r="H40" s="5" t="n">
+      <c r="H40" s="3" t="n">
         <v>-2.4</v>
       </c>
       <c r="I40" t="n">
@@ -3729,7 +3891,7 @@
       <c r="G49" t="n">
         <v>12.5</v>
       </c>
-      <c r="H49" s="5" t="n">
+      <c r="H49" s="3" t="n">
         <v>-5.5</v>
       </c>
       <c r="I49" t="n">
@@ -3867,7 +4029,7 @@
       <c r="G52" t="n">
         <v>9.5</v>
       </c>
-      <c r="H52" s="5" t="n">
+      <c r="H52" s="3" t="n">
         <v>-2.5</v>
       </c>
       <c r="I52" t="n">
@@ -4189,7 +4351,7 @@
       <c r="G59" t="n">
         <v>9.1</v>
       </c>
-      <c r="H59" s="5" t="n">
+      <c r="H59" s="3" t="n">
         <v>-3.1</v>
       </c>
       <c r="I59" t="n">
@@ -4235,7 +4397,7 @@
       <c r="G60" t="n">
         <v>8.9</v>
       </c>
-      <c r="H60" s="5" t="n">
+      <c r="H60" s="3" t="n">
         <v>-2.9</v>
       </c>
       <c r="I60" t="n">
@@ -4281,7 +4443,7 @@
       <c r="G61" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="H61" s="5" t="n">
+      <c r="H61" s="3" t="n">
         <v>-2.2</v>
       </c>
       <c r="I61" t="n">
@@ -4327,7 +4489,7 @@
       <c r="G62" t="n">
         <v>10.1</v>
       </c>
-      <c r="H62" s="5" t="n">
+      <c r="H62" s="3" t="n">
         <v>-4.1</v>
       </c>
       <c r="I62" t="n">
@@ -4373,7 +4535,7 @@
       <c r="G63" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="H63" s="5" t="n">
+      <c r="H63" s="3" t="n">
         <v>-2.3</v>
       </c>
       <c r="I63" t="n">
@@ -4603,7 +4765,7 @@
       <c r="G68" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="H68" s="5" t="n">
+      <c r="H68" s="3" t="n">
         <v>-2.3</v>
       </c>
       <c r="I68" t="n">
@@ -4649,7 +4811,7 @@
       <c r="G69" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="H69" s="5" t="n">
+      <c r="H69" s="3" t="n">
         <v>-2.2</v>
       </c>
       <c r="I69" t="n">
@@ -4787,7 +4949,7 @@
       <c r="G72" t="n">
         <v>10.2</v>
       </c>
-      <c r="H72" s="5" t="n">
+      <c r="H72" s="3" t="n">
         <v>-5.2</v>
       </c>
       <c r="I72" t="n">
@@ -4833,7 +4995,7 @@
       <c r="G73" t="n">
         <v>11.4</v>
       </c>
-      <c r="H73" s="5" t="n">
+      <c r="H73" s="3" t="n">
         <v>-6.4</v>
       </c>
       <c r="I73" t="n">
@@ -4879,7 +5041,7 @@
       <c r="G74" t="n">
         <v>7.4</v>
       </c>
-      <c r="H74" s="5" t="n">
+      <c r="H74" s="3" t="n">
         <v>-2.4</v>
       </c>
       <c r="I74" t="n">
@@ -4925,7 +5087,7 @@
       <c r="G75" t="n">
         <v>7</v>
       </c>
-      <c r="H75" s="5" t="n">
+      <c r="H75" s="3" t="n">
         <v>-2</v>
       </c>
       <c r="I75" t="n">
@@ -4971,7 +5133,7 @@
       <c r="G76" t="n">
         <v>8</v>
       </c>
-      <c r="H76" s="5" t="n">
+      <c r="H76" s="3" t="n">
         <v>-3</v>
       </c>
       <c r="I76" t="n">
@@ -5109,7 +5271,7 @@
       <c r="G79" t="n">
         <v>8.6</v>
       </c>
-      <c r="H79" s="5" t="n">
+      <c r="H79" s="3" t="n">
         <v>-3.6</v>
       </c>
       <c r="I79" t="n">
@@ -5201,7 +5363,7 @@
       <c r="G81" t="n">
         <v>8.9</v>
       </c>
-      <c r="H81" s="5" t="n">
+      <c r="H81" s="3" t="n">
         <v>-4.9</v>
       </c>
       <c r="I81" t="n">
@@ -5247,7 +5409,7 @@
       <c r="G82" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="H82" s="5" t="n">
+      <c r="H82" s="3" t="n">
         <v>-4.7</v>
       </c>
       <c r="I82" t="n">
@@ -5293,7 +5455,7 @@
       <c r="G83" t="n">
         <v>6.6</v>
       </c>
-      <c r="H83" s="5" t="n">
+      <c r="H83" s="3" t="n">
         <v>-2.6</v>
       </c>
       <c r="I83" t="n">
@@ -5339,7 +5501,7 @@
       <c r="G84" t="n">
         <v>7.3</v>
       </c>
-      <c r="H84" s="5" t="n">
+      <c r="H84" s="3" t="n">
         <v>-3.3</v>
       </c>
       <c r="I84" t="n">
@@ -5385,7 +5547,7 @@
       <c r="G85" t="n">
         <v>7.1</v>
       </c>
-      <c r="H85" s="5" t="n">
+      <c r="H85" s="3" t="n">
         <v>-3.1</v>
       </c>
       <c r="I85" t="n">
@@ -5431,7 +5593,7 @@
       <c r="G86" t="n">
         <v>9</v>
       </c>
-      <c r="H86" s="5" t="n">
+      <c r="H86" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="I86" t="n">
@@ -5477,7 +5639,7 @@
       <c r="G87" t="n">
         <v>6.1</v>
       </c>
-      <c r="H87" s="5" t="n">
+      <c r="H87" s="3" t="n">
         <v>-2.1</v>
       </c>
       <c r="I87" t="n">
@@ -5707,7 +5869,7 @@
       <c r="G92" t="n">
         <v>10.1</v>
       </c>
-      <c r="H92" s="5" t="n">
+      <c r="H92" s="3" t="n">
         <v>-7.1</v>
       </c>
       <c r="I92" t="n">
@@ -5753,7 +5915,7 @@
       <c r="G93" t="n">
         <v>7.8</v>
       </c>
-      <c r="H93" s="5" t="n">
+      <c r="H93" s="3" t="n">
         <v>-4.8</v>
       </c>
       <c r="I93" t="n">
@@ -5799,7 +5961,7 @@
       <c r="G94" t="n">
         <v>6.1</v>
       </c>
-      <c r="H94" s="5" t="n">
+      <c r="H94" s="3" t="n">
         <v>-3.1</v>
       </c>
       <c r="I94" t="n">
@@ -5845,7 +6007,7 @@
       <c r="G95" t="n">
         <v>7.3</v>
       </c>
-      <c r="H95" s="5" t="n">
+      <c r="H95" s="3" t="n">
         <v>-4.3</v>
       </c>
       <c r="I95" t="n">
@@ -5937,7 +6099,7 @@
       <c r="G97" t="n">
         <v>5.6</v>
       </c>
-      <c r="H97" s="5" t="n">
+      <c r="H97" s="3" t="n">
         <v>-2.6</v>
       </c>
       <c r="I97" t="n">
@@ -5983,7 +6145,7 @@
       <c r="G98" t="n">
         <v>6.4</v>
       </c>
-      <c r="H98" s="5" t="n">
+      <c r="H98" s="3" t="n">
         <v>-3.4</v>
       </c>
       <c r="I98" t="n">
@@ -6029,7 +6191,7 @@
       <c r="G99" t="n">
         <v>6.2</v>
       </c>
-      <c r="H99" s="5" t="n">
+      <c r="H99" s="3" t="n">
         <v>-3.2</v>
       </c>
       <c r="I99" t="n">
@@ -6075,7 +6237,7 @@
       <c r="G100" t="n">
         <v>7.3</v>
       </c>
-      <c r="H100" s="5" t="n">
+      <c r="H100" s="3" t="n">
         <v>-5.3</v>
       </c>
       <c r="I100" t="n">
@@ -6121,7 +6283,7 @@
       <c r="G101" t="n">
         <v>7.5</v>
       </c>
-      <c r="H101" s="5" t="n">
+      <c r="H101" s="3" t="n">
         <v>-5.5</v>
       </c>
       <c r="I101" t="n">
@@ -6167,7 +6329,7 @@
       <c r="G102" t="n">
         <v>4.9</v>
       </c>
-      <c r="H102" s="5" t="n">
+      <c r="H102" s="3" t="n">
         <v>-2.9</v>
       </c>
       <c r="I102" t="n">
@@ -6213,7 +6375,7 @@
       <c r="G103" t="n">
         <v>4.3</v>
       </c>
-      <c r="H103" s="5" t="n">
+      <c r="H103" s="3" t="n">
         <v>-2.3</v>
       </c>
       <c r="I103" t="n">
@@ -6259,7 +6421,7 @@
       <c r="G104" t="n">
         <v>4.5</v>
       </c>
-      <c r="H104" s="5" t="n">
+      <c r="H104" s="3" t="n">
         <v>-2.5</v>
       </c>
       <c r="I104" t="n">
@@ -6305,7 +6467,7 @@
       <c r="G105" t="n">
         <v>9.300000000000001</v>
       </c>
-      <c r="H105" s="5" t="n">
+      <c r="H105" s="3" t="n">
         <v>-8.300000000000001</v>
       </c>
       <c r="I105" t="n">
@@ -6351,7 +6513,7 @@
       <c r="G106" t="n">
         <v>7.4</v>
       </c>
-      <c r="H106" s="5" t="n">
+      <c r="H106" s="3" t="n">
         <v>-6.4</v>
       </c>
       <c r="I106" t="n">
@@ -6397,7 +6559,7 @@
       <c r="G107" t="n">
         <v>8</v>
       </c>
-      <c r="H107" s="5" t="n">
+      <c r="H107" s="3" t="n">
         <v>-7</v>
       </c>
       <c r="I107" t="n">
@@ -6443,7 +6605,7 @@
       <c r="G108" t="n">
         <v>6.5</v>
       </c>
-      <c r="H108" s="5" t="n">
+      <c r="H108" s="3" t="n">
         <v>-5.5</v>
       </c>
       <c r="I108" t="n">
@@ -6489,7 +6651,7 @@
       <c r="G109" t="n">
         <v>4.2</v>
       </c>
-      <c r="H109" s="5" t="n">
+      <c r="H109" s="3" t="n">
         <v>-3.2</v>
       </c>
       <c r="I109" t="n">
@@ -6535,7 +6697,7 @@
       <c r="G110" t="n">
         <v>7.1</v>
       </c>
-      <c r="H110" s="5" t="n">
+      <c r="H110" s="3" t="n">
         <v>-7.1</v>
       </c>
       <c r="I110" t="n">
@@ -6581,7 +6743,7 @@
       <c r="G111" t="n">
         <v>6.4</v>
       </c>
-      <c r="H111" s="5" t="n">
+      <c r="H111" s="3" t="n">
         <v>-6.4</v>
       </c>
       <c r="I111" t="n">
@@ -6627,7 +6789,7 @@
       <c r="G112" t="n">
         <v>5.7</v>
       </c>
-      <c r="H112" s="5" t="n">
+      <c r="H112" s="3" t="n">
         <v>-5.7</v>
       </c>
       <c r="I112" t="n">
@@ -6673,7 +6835,7 @@
       <c r="G113" t="n">
         <v>6.2</v>
       </c>
-      <c r="H113" s="5" t="n">
+      <c r="H113" s="3" t="n">
         <v>-6.2</v>
       </c>
       <c r="I113" t="n">
@@ -6719,7 +6881,7 @@
       <c r="G114" t="n">
         <v>5.7</v>
       </c>
-      <c r="H114" s="5" t="n">
+      <c r="H114" s="3" t="n">
         <v>-5.7</v>
       </c>
       <c r="I114" t="n">
@@ -6765,7 +6927,7 @@
       <c r="G115" t="n">
         <v>7.1</v>
       </c>
-      <c r="H115" s="5" t="n">
+      <c r="H115" s="3" t="n">
         <v>-8.1</v>
       </c>
       <c r="I115" t="n">
@@ -7211,7 +7373,7 @@
       <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
@@ -7238,7 +7400,7 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>OUT: Xross</t>
+          <t>OUT: Marteen</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
@@ -7282,7 +7444,7 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>OUT: Marteen</t>
+          <t>OUT: Xross</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
@@ -7695,7 +7857,7 @@
       <c r="H31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="inlineStr">
+      <c r="A32" s="5" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
@@ -7722,7 +7884,7 @@
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>OUT: Lovers rock</t>
+          <t>OUT: Krostaly</t>
         </is>
       </c>
       <c r="C35" s="7" t="inlineStr">
@@ -7744,7 +7906,7 @@
       </c>
       <c r="B36" s="7" t="inlineStr">
         <is>
-          <t>OUT: Krostaly</t>
+          <t>OUT: Jemkin</t>
         </is>
       </c>
       <c r="C36" s="7" t="inlineStr">
@@ -7766,7 +7928,7 @@
       </c>
       <c r="B37" s="7" t="inlineStr">
         <is>
-          <t>OUT: Jemkin</t>
+          <t>OUT: Lovers rock</t>
         </is>
       </c>
       <c r="C37" s="7" t="inlineStr">
@@ -8179,7 +8341,7 @@
       <c r="H49" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="3" t="inlineStr">
+      <c r="A50" s="5" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
@@ -8206,7 +8368,7 @@
       </c>
       <c r="B53" s="7" t="inlineStr">
         <is>
-          <t>OUT: Loita</t>
+          <t>OUT: Stax</t>
         </is>
       </c>
       <c r="C53" s="7" t="inlineStr">
@@ -8228,7 +8390,7 @@
       </c>
       <c r="B54" s="7" t="inlineStr">
         <is>
-          <t>OUT: Primmie</t>
+          <t>OUT: Loita</t>
         </is>
       </c>
       <c r="C54" s="7" t="inlineStr">
@@ -8250,7 +8412,7 @@
       </c>
       <c r="B55" s="7" t="inlineStr">
         <is>
-          <t>OUT: Stax</t>
+          <t>OUT: Primmie</t>
         </is>
       </c>
       <c r="C55" s="7" t="inlineStr">
@@ -8663,7 +8825,7 @@
       <c r="H67" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" s="3" t="inlineStr">
+      <c r="A68" s="5" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
@@ -8690,7 +8852,7 @@
       </c>
       <c r="B71" s="7" t="inlineStr">
         <is>
-          <t>OUT: seven</t>
+          <t>OUT: Veqaj</t>
         </is>
       </c>
       <c r="C71" s="7" t="inlineStr">
@@ -8712,7 +8874,7 @@
       </c>
       <c r="B72" s="7" t="inlineStr">
         <is>
-          <t>OUT: Veqaj</t>
+          <t>OUT: seven</t>
         </is>
       </c>
       <c r="C72" s="7" t="inlineStr">
@@ -9147,7 +9309,7 @@
       <c r="H85" t="inlineStr"/>
     </row>
     <row r="86">
-      <c r="A86" s="3" t="inlineStr">
+      <c r="A86" s="5" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
@@ -9174,7 +9336,7 @@
       </c>
       <c r="B89" s="7" t="inlineStr">
         <is>
-          <t>OUT: Udotan</t>
+          <t>OUT: Killua</t>
         </is>
       </c>
       <c r="C89" s="7" t="inlineStr">
@@ -9218,7 +9380,7 @@
       </c>
       <c r="B91" s="7" t="inlineStr">
         <is>
-          <t>OUT: Killua</t>
+          <t>OUT: Udotan</t>
         </is>
       </c>
       <c r="C91" s="7" t="inlineStr">
@@ -9631,7 +9793,7 @@
       <c r="H103" t="inlineStr"/>
     </row>
     <row r="104">
-      <c r="A104" s="3" t="inlineStr">
+      <c r="A104" s="5" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
@@ -10073,7 +10235,7 @@
       <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
@@ -10100,7 +10262,7 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>OUT: PROFEK</t>
+          <t>OUT: Munchkin</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
@@ -10122,7 +10284,7 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>OUT: Munchkin</t>
+          <t>OUT: xeus</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
@@ -10144,7 +10306,7 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>OUT: xeus</t>
+          <t>OUT: PROFEK</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
@@ -10557,7 +10719,7 @@
       <c r="H31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="inlineStr">
+      <c r="A32" s="5" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
@@ -10584,7 +10746,7 @@
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>OUT: Yetujey</t>
+          <t>OUT: Kushy</t>
         </is>
       </c>
       <c r="C35" s="7" t="inlineStr">
@@ -10606,7 +10768,7 @@
       </c>
       <c r="B36" s="7" t="inlineStr">
         <is>
-          <t>OUT: Kushy</t>
+          <t>OUT: Lar0k</t>
         </is>
       </c>
       <c r="C36" s="7" t="inlineStr">
@@ -10628,7 +10790,7 @@
       </c>
       <c r="B37" s="7" t="inlineStr">
         <is>
-          <t>OUT: Lar0k</t>
+          <t>OUT: Yetujey</t>
         </is>
       </c>
       <c r="C37" s="7" t="inlineStr">
@@ -11041,7 +11203,7 @@
       <c r="H49" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="3" t="inlineStr">
+      <c r="A50" s="5" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
@@ -11068,7 +11230,7 @@
       </c>
       <c r="B53" s="7" t="inlineStr">
         <is>
-          <t>OUT: Jemkin</t>
+          <t>OUT: BeYN</t>
         </is>
       </c>
       <c r="C53" s="7" t="inlineStr">
@@ -11090,7 +11252,7 @@
       </c>
       <c r="B54" s="7" t="inlineStr">
         <is>
-          <t>OUT: Udotan</t>
+          <t>OUT: Jemkin</t>
         </is>
       </c>
       <c r="C54" s="7" t="inlineStr">
@@ -11112,7 +11274,7 @@
       </c>
       <c r="B55" s="7" t="inlineStr">
         <is>
-          <t>OUT: BeYN</t>
+          <t>OUT: Udotan</t>
         </is>
       </c>
       <c r="C55" s="7" t="inlineStr">
@@ -11525,7 +11687,7 @@
       <c r="H67" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" s="3" t="inlineStr">
+      <c r="A68" s="5" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
@@ -11574,7 +11736,7 @@
       </c>
       <c r="B72" s="7" t="inlineStr">
         <is>
-          <t>OUT: Veqaj</t>
+          <t>OUT: Patmen</t>
         </is>
       </c>
       <c r="C72" s="7" t="inlineStr">
@@ -11596,7 +11758,7 @@
       </c>
       <c r="B73" s="7" t="inlineStr">
         <is>
-          <t>OUT: Patmen</t>
+          <t>OUT: Veqaj</t>
         </is>
       </c>
       <c r="C73" s="7" t="inlineStr">
@@ -12009,7 +12171,7 @@
       <c r="H85" t="inlineStr"/>
     </row>
     <row r="86">
-      <c r="A86" s="3" t="inlineStr">
+      <c r="A86" s="5" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
@@ -12058,7 +12220,7 @@
       </c>
       <c r="B90" s="7" t="inlineStr">
         <is>
-          <t>OUT: Primmie</t>
+          <t>OUT: Killua</t>
         </is>
       </c>
       <c r="C90" s="7" t="inlineStr">
@@ -12080,7 +12242,7 @@
       </c>
       <c r="B91" s="7" t="inlineStr">
         <is>
-          <t>OUT: Killua</t>
+          <t>OUT: Primmie</t>
         </is>
       </c>
       <c r="C91" s="7" t="inlineStr">
@@ -12493,7 +12655,7 @@
       <c r="H103" t="inlineStr"/>
     </row>
     <row r="104">
-      <c r="A104" s="3" t="inlineStr">
+      <c r="A104" s="5" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
@@ -12935,7 +13097,7 @@
       <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
@@ -12962,7 +13124,7 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>OUT: Lar0k</t>
+          <t>OUT: Jemkin</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
@@ -13006,7 +13168,7 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>OUT: Jemkin</t>
+          <t>OUT: Lar0k</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
@@ -13419,7 +13581,7 @@
       <c r="H31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="inlineStr">
+      <c r="A32" s="5" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
@@ -13446,7 +13608,7 @@
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>OUT: PROFEK</t>
+          <t>OUT: Kushy</t>
         </is>
       </c>
       <c r="C35" s="7" t="inlineStr">
@@ -13468,7 +13630,7 @@
       </c>
       <c r="B36" s="7" t="inlineStr">
         <is>
-          <t>OUT: Kushy</t>
+          <t>OUT: xeus</t>
         </is>
       </c>
       <c r="C36" s="7" t="inlineStr">
@@ -13490,7 +13652,7 @@
       </c>
       <c r="B37" s="7" t="inlineStr">
         <is>
-          <t>OUT: xeus</t>
+          <t>OUT: PROFEK</t>
         </is>
       </c>
       <c r="C37" s="7" t="inlineStr">
@@ -13903,7 +14065,7 @@
       <c r="H49" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="3" t="inlineStr">
+      <c r="A50" s="5" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
@@ -13930,7 +14092,7 @@
       </c>
       <c r="B53" s="7" t="inlineStr">
         <is>
-          <t>OUT: Yetujey</t>
+          <t>OUT: BeYN</t>
         </is>
       </c>
       <c r="C53" s="7" t="inlineStr">
@@ -13974,7 +14136,7 @@
       </c>
       <c r="B55" s="7" t="inlineStr">
         <is>
-          <t>OUT: BeYN</t>
+          <t>OUT: Yetujey</t>
         </is>
       </c>
       <c r="C55" s="7" t="inlineStr">
@@ -14387,7 +14549,7 @@
       <c r="H67" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" s="3" t="inlineStr">
+      <c r="A68" s="5" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
@@ -14436,7 +14598,7 @@
       </c>
       <c r="B72" s="7" t="inlineStr">
         <is>
-          <t>OUT: Rosé</t>
+          <t>OUT: Killua</t>
         </is>
       </c>
       <c r="C72" s="7" t="inlineStr">
@@ -14458,7 +14620,7 @@
       </c>
       <c r="B73" s="7" t="inlineStr">
         <is>
-          <t>OUT: Killua</t>
+          <t>OUT: Rosé</t>
         </is>
       </c>
       <c r="C73" s="7" t="inlineStr">
@@ -14871,7 +15033,7 @@
       <c r="H85" t="inlineStr"/>
     </row>
     <row r="86">
-      <c r="A86" s="3" t="inlineStr">
+      <c r="A86" s="5" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
@@ -14898,7 +15060,7 @@
       </c>
       <c r="B89" s="7" t="inlineStr">
         <is>
-          <t>OUT: Derke</t>
+          <t>OUT: Patmen</t>
         </is>
       </c>
       <c r="C89" s="7" t="inlineStr">
@@ -14942,7 +15104,7 @@
       </c>
       <c r="B91" s="7" t="inlineStr">
         <is>
-          <t>OUT: Patmen</t>
+          <t>OUT: Derke</t>
         </is>
       </c>
       <c r="C91" s="7" t="inlineStr">
@@ -15355,7 +15517,7 @@
       <c r="H103" t="inlineStr"/>
     </row>
     <row r="104">
-      <c r="A104" s="3" t="inlineStr">
+      <c r="A104" s="5" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>

--- a/output/VFL_2026_Stage1_W1_Report.xlsx
+++ b/output/VFL_2026_Stage1_W1_Report.xlsx
@@ -1325,10 +1325,10 @@
         <v>9.4</v>
       </c>
       <c r="H6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>4.6</v>
+        <v>5.6</v>
       </c>
       <c r="J6" t="n">
         <v>9.4</v>
@@ -1368,10 +1368,10 @@
         <v>7.7</v>
       </c>
       <c r="H7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3</v>
+        <v>1.3</v>
       </c>
       <c r="J7" t="n">
         <v>7.7</v>
@@ -1603,7 +1603,7 @@
         <v>100</v>
       </c>
       <c r="H14" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="J14" t="n">
         <v>105.9</v>
@@ -1748,17 +1748,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Jemkin</t>
+          <t>Derke</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Rex Regum Qeon</t>
+          <t>Team Vitality</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>PAC</t>
+          <t>EMEA</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1767,39 +1767,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="F3" t="n">
         <v>15</v>
       </c>
       <c r="G3" t="n">
-        <v>10.7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>4.3</v>
+        <v>5.8</v>
       </c>
       <c r="I3" t="n">
-        <v>1.38</v>
+        <v>1.59</v>
       </c>
       <c r="J3" t="n">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="K3" t="n">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="L3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Ruxic</t>
+          <t>Alfajer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Natus Vincere</t>
+          <t>FNATIC</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1809,29 +1809,29 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="F4" t="n">
         <v>15</v>
       </c>
       <c r="G4" t="n">
-        <v>8.199999999999999</v>
+        <v>10.6</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>6.8</v>
+        <v>4.4</v>
       </c>
       <c r="I4" t="n">
-        <v>1.36</v>
+        <v>1.17</v>
       </c>
       <c r="J4" t="n">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="K4" t="n">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="L4" t="n">
         <v>3</v>
@@ -1840,17 +1840,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Derke</t>
+          <t>Jemkin</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Team Vitality</t>
+          <t>Rex Regum Qeon</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>EMEA</t>
+          <t>PAC</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1859,39 +1859,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="F5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G5" t="n">
-        <v>9.199999999999999</v>
+        <v>10.7</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="I5" t="n">
-        <v>1.59</v>
+        <v>1.38</v>
       </c>
       <c r="J5" t="n">
-        <v>37</v>
+        <v>58</v>
       </c>
       <c r="K5" t="n">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="L5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Alfajer</t>
+          <t>Ruxic</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>FNATIC</t>
+          <t>Natus Vincere</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1901,29 +1901,29 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="F6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G6" t="n">
-        <v>10.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>3.4</v>
+        <v>6.8</v>
       </c>
       <c r="I6" t="n">
-        <v>1.17</v>
+        <v>1.36</v>
       </c>
       <c r="J6" t="n">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="K6" t="n">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="L6" t="n">
         <v>3</v>
@@ -1932,72 +1932,72 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Primmie</t>
+          <t>Veqaj</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>FULL SENSE</t>
+          <t>FNATIC</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>PAC</t>
+          <t>EMEA</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>13.5</v>
+        <v>10.5</v>
       </c>
       <c r="F7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G7" t="n">
         <v>9.4</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>4.6</v>
+        <v>5.6</v>
       </c>
       <c r="I7" t="n">
-        <v>1.54</v>
+        <v>1.21</v>
       </c>
       <c r="J7" t="n">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="K7" t="n">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="L7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Veqaj</t>
+          <t>Primmie</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>FNATIC</t>
+          <t>FULL SENSE</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>EMEA</t>
+          <t>PAC</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>10.5</v>
+        <v>13.5</v>
       </c>
       <c r="F8" t="n">
         <v>14</v>
@@ -2009,16 +2009,16 @@
         <v>4.6</v>
       </c>
       <c r="I8" t="n">
-        <v>1.21</v>
+        <v>1.54</v>
       </c>
       <c r="J8" t="n">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="K8" t="n">
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="L8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -2070,22 +2070,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Patmen</t>
+          <t>Sayonara</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Global Esports</t>
+          <t>Team Vitality</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>PAC</t>
+          <t>EMEA</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>I</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -2095,19 +2095,19 @@
         <v>13</v>
       </c>
       <c r="G10" t="n">
-        <v>8.300000000000001</v>
+        <v>7.3</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>4.7</v>
+        <v>5.7</v>
       </c>
       <c r="I10" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="J10" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="K10" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="L10" t="n">
         <v>2</v>
@@ -2116,63 +2116,63 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Filu</t>
+          <t>Patmen</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Natus Vincere</t>
+          <t>Global Esports</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>EMEA</t>
+          <t>PAC</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F11" t="n">
         <v>13</v>
       </c>
       <c r="G11" t="n">
-        <v>5.7</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>7.3</v>
+        <v>4.7</v>
       </c>
       <c r="I11" t="n">
-        <v>1.2</v>
+        <v>1.49</v>
       </c>
       <c r="J11" t="n">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="K11" t="n">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="L11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>something</t>
+          <t>Filu</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Paper Rex</t>
+          <t>Natus Vincere</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>PAC</t>
+          <t>EMEA</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2181,25 +2181,25 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>13.5</v>
+        <v>9</v>
       </c>
       <c r="F12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G12" t="n">
-        <v>8.300000000000001</v>
+        <v>5.7</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>3.7</v>
+        <v>7.3</v>
       </c>
       <c r="I12" t="n">
-        <v>1.09</v>
+        <v>1.2</v>
       </c>
       <c r="J12" t="n">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="K12" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="L12" t="n">
         <v>3</v>
@@ -2208,17 +2208,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>HYUNMIN</t>
+          <t>Kaajak</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>DRX</t>
+          <t>FNATIC</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>PAC</t>
+          <t>EMEA</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2227,85 +2227,85 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="F13" t="n">
         <v>12</v>
       </c>
       <c r="G13" t="n">
-        <v>10.3</v>
+        <v>10.9</v>
       </c>
       <c r="H13" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="I13" t="n">
-        <v>1.31</v>
+        <v>0.95</v>
       </c>
       <c r="J13" t="n">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="K13" t="n">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="L13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Sayonara</t>
+          <t>something</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Team Vitality</t>
+          <t>Paper Rex</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>EMEA</t>
+          <t>PAC</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>10</v>
+        <v>13.5</v>
       </c>
       <c r="F14" t="n">
         <v>12</v>
       </c>
       <c r="G14" t="n">
-        <v>7.3</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>4.7</v>
+        <v>3.7</v>
       </c>
       <c r="I14" t="n">
-        <v>1.47</v>
+        <v>1.09</v>
       </c>
       <c r="J14" t="n">
-        <v>32</v>
+        <v>56</v>
       </c>
       <c r="K14" t="n">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="L14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Udotan</t>
+          <t>HYUNMIN</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Global Esports</t>
+          <t>DRX</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2315,29 +2315,29 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F15" t="n">
         <v>12</v>
       </c>
       <c r="G15" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="H15" s="4" t="n">
-        <v>4.3</v>
+        <v>10.3</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.7</v>
       </c>
       <c r="I15" t="n">
-        <v>1.13</v>
+        <v>1.31</v>
       </c>
       <c r="J15" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="K15" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="L15" t="n">
         <v>2</v>
@@ -2346,47 +2346,47 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Kaajak</t>
+          <t>Udotan</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>FNATIC</t>
+          <t>Global Esports</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>EMEA</t>
+          <t>PAC</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>14.5</v>
+        <v>9</v>
       </c>
       <c r="F16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G16" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0.1</v>
+        <v>7.7</v>
+      </c>
+      <c r="H16" s="4" t="n">
+        <v>4.3</v>
       </c>
       <c r="I16" t="n">
-        <v>0.95</v>
+        <v>1.13</v>
       </c>
       <c r="J16" t="n">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="K16" t="n">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="L16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -2484,17 +2484,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Killua</t>
+          <t>Crashies</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>FULL SENSE</t>
+          <t>FNATIC</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>PAC</t>
+          <t>EMEA</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2503,39 +2503,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F19" t="n">
         <v>11</v>
       </c>
       <c r="G19" t="n">
-        <v>7.5</v>
+        <v>9</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="I19" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="J19" t="n">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="K19" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="L19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>f0rsaken</t>
+          <t>Killua</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Paper Rex</t>
+          <t>FULL SENSE</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2545,38 +2545,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>I</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>13.5</v>
+        <v>8</v>
       </c>
       <c r="F20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G20" t="n">
-        <v>9</v>
-      </c>
-      <c r="H20" t="n">
-        <v>1</v>
+        <v>7.5</v>
+      </c>
+      <c r="H20" s="4" t="n">
+        <v>3.5</v>
       </c>
       <c r="I20" t="n">
-        <v>1.05</v>
+        <v>1.25</v>
       </c>
       <c r="J20" t="n">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="K20" t="n">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="L20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>invy</t>
+          <t>f0rsaken</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2591,29 +2591,29 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="F21" t="n">
         <v>10</v>
       </c>
       <c r="G21" t="n">
-        <v>8.1</v>
+        <v>9</v>
       </c>
       <c r="H21" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="I21" t="n">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="J21" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="K21" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="L21" t="n">
         <v>3</v>
@@ -2622,44 +2622,44 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>xeus</t>
+          <t>invy</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>FUT Esports</t>
+          <t>Paper Rex</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>EMEA</t>
+          <t>PAC</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>I</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="F22" t="n">
         <v>10</v>
       </c>
       <c r="G22" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="H22" s="4" t="n">
-        <v>2.4</v>
+        <v>8.1</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.9</v>
       </c>
       <c r="I22" t="n">
-        <v>1.02</v>
+        <v>1.13</v>
       </c>
       <c r="J22" t="n">
         <v>51</v>
       </c>
       <c r="K22" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L22" t="n">
         <v>3</v>
@@ -2668,44 +2668,44 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Ivy</t>
+          <t>xeus</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>NOngshim RedForce</t>
+          <t>FUT Esports</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>PAC</t>
+          <t>EMEA</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="F23" t="n">
         <v>10</v>
       </c>
       <c r="G23" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="H23" t="n">
-        <v>1.2</v>
+        <v>7.6</v>
+      </c>
+      <c r="H23" s="4" t="n">
+        <v>2.4</v>
       </c>
       <c r="I23" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="J23" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="K23" t="n">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="L23" t="n">
         <v>3</v>
@@ -2714,44 +2714,44 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Crashies</t>
+          <t>Ivy</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>FNATIC</t>
+          <t>NOngshim RedForce</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>EMEA</t>
+          <t>PAC</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F24" t="n">
         <v>10</v>
       </c>
       <c r="G24" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H24" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="I24" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="J24" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K24" t="n">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="L24" t="n">
         <v>3</v>
@@ -3312,12 +3312,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Rosé</t>
+          <t>Jamppi</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>BBL Esports</t>
+          <t>Team Vitality</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -3331,25 +3331,25 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>7</v>
+        <v>8.5</v>
       </c>
       <c r="F37" t="n">
         <v>9</v>
       </c>
       <c r="G37" t="n">
-        <v>8.4</v>
+        <v>7.2</v>
       </c>
       <c r="H37" t="n">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="I37" t="n">
-        <v>1.13</v>
+        <v>1.23</v>
       </c>
       <c r="J37" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="K37" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="L37" t="n">
         <v>2</v>
@@ -3358,17 +3358,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>crazyguy</t>
+          <t>PROFEK</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Rex Regum Qeon</t>
+          <t>Team Vitality</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>PAC</t>
+          <t>EMEA</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -3377,39 +3377,39 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>7</v>
+        <v>8.5</v>
       </c>
       <c r="F38" t="n">
         <v>9</v>
       </c>
       <c r="G38" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="H38" s="4" t="n">
-        <v>2.9</v>
+        <v>7.7</v>
+      </c>
+      <c r="H38" t="n">
+        <v>1.3</v>
       </c>
       <c r="I38" t="n">
         <v>1.12</v>
       </c>
       <c r="J38" t="n">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="K38" t="n">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="L38" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Marteen</t>
+          <t>Rosé</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Gentle Mates</t>
+          <t>BBL Esports</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -3419,121 +3419,121 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>I</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="F39" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G39" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="H39" s="3" t="n">
-        <v>-4.3</v>
+        <v>8.4</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.6</v>
       </c>
       <c r="I39" t="n">
-        <v>0.89</v>
+        <v>1.13</v>
       </c>
       <c r="J39" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="K39" t="n">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="L39" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Meteor</t>
+          <t>Boaster</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>FNATIC</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>PAC</t>
+          <t>EMEA</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="F40" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G40" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="H40" s="3" t="n">
-        <v>-2.4</v>
+        <v>5.7</v>
+      </c>
+      <c r="H40" s="4" t="n">
+        <v>3.3</v>
       </c>
       <c r="I40" t="n">
-        <v>1.26</v>
+        <v>0.97</v>
       </c>
       <c r="J40" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K40" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="L40" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Wo0t</t>
+          <t>crazyguy</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Team Heretics</t>
+          <t>Rex Regum Qeon</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>EMEA</t>
+          <t>PAC</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>10.5</v>
+        <v>7</v>
       </c>
       <c r="F41" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G41" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="H41" t="n">
-        <v>0.7</v>
+        <v>6.1</v>
+      </c>
+      <c r="H41" s="4" t="n">
+        <v>2.9</v>
       </c>
       <c r="I41" t="n">
-        <v>0.78</v>
+        <v>1.12</v>
       </c>
       <c r="J41" t="n">
         <v>44</v>
       </c>
       <c r="K41" t="n">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="L41" t="n">
         <v>3</v>
@@ -3542,12 +3542,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Jamppi</t>
+          <t>Marteen</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Team Vitality</t>
+          <t>Gentle Mates</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3557,75 +3557,75 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>8.5</v>
+        <v>15</v>
       </c>
       <c r="F42" t="n">
         <v>8</v>
       </c>
       <c r="G42" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="H42" t="n">
-        <v>0.8</v>
+        <v>12.3</v>
+      </c>
+      <c r="H42" s="3" t="n">
+        <v>-4.3</v>
       </c>
       <c r="I42" t="n">
-        <v>1.23</v>
+        <v>0.89</v>
       </c>
       <c r="J42" t="n">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="K42" t="n">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="L42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>PROFEK</t>
+          <t>Meteor</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Team Vitality</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>EMEA</t>
+          <t>PAC</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>8.5</v>
+        <v>12</v>
       </c>
       <c r="F43" t="n">
         <v>8</v>
       </c>
       <c r="G43" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="H43" t="n">
-        <v>0.3</v>
+        <v>10.4</v>
+      </c>
+      <c r="H43" s="3" t="n">
+        <v>-2.4</v>
       </c>
       <c r="I43" t="n">
-        <v>1.12</v>
+        <v>1.26</v>
       </c>
       <c r="J43" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="K43" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L43" t="n">
         <v>2</v>
@@ -3634,12 +3634,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Dos9</t>
+          <t>Wo0t</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Karmine Corp</t>
+          <t>Team Heretics</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3649,75 +3649,75 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>I</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>8</v>
+        <v>10.5</v>
       </c>
       <c r="F44" t="n">
         <v>8</v>
       </c>
       <c r="G44" t="n">
-        <v>6.8</v>
+        <v>7.3</v>
       </c>
       <c r="H44" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="I44" t="n">
-        <v>1.26</v>
+        <v>0.78</v>
       </c>
       <c r="J44" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="K44" t="n">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="L44" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Jitboys</t>
+          <t>Dos9</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>FULL SENSE</t>
+          <t>Karmine Corp</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>PAC</t>
+          <t>EMEA</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="F45" t="n">
         <v>8</v>
       </c>
       <c r="G45" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="H45" s="4" t="n">
-        <v>2.4</v>
+        <v>6.8</v>
+      </c>
+      <c r="H45" t="n">
+        <v>1.2</v>
       </c>
       <c r="I45" t="n">
-        <v>0.95</v>
+        <v>1.26</v>
       </c>
       <c r="J45" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="K45" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="L45" t="n">
         <v>2</v>
@@ -3726,12 +3726,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>BeYN</t>
+          <t>Jitboys</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>DRX</t>
+          <t>FULL SENSE</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E46" t="n">
@@ -3751,19 +3751,19 @@
         <v>8</v>
       </c>
       <c r="G46" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="H46" t="n">
-        <v>0.6</v>
+        <v>5.6</v>
+      </c>
+      <c r="H46" s="4" t="n">
+        <v>2.4</v>
       </c>
       <c r="I46" t="n">
-        <v>1.24</v>
+        <v>0.95</v>
       </c>
       <c r="J46" t="n">
+        <v>32</v>
+      </c>
+      <c r="K46" t="n">
         <v>33</v>
-      </c>
-      <c r="K46" t="n">
-        <v>27</v>
       </c>
       <c r="L46" t="n">
         <v>2</v>
@@ -3772,17 +3772,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>purp0</t>
+          <t>BeYN</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Team Liquid</t>
+          <t>DRX</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>EMEA</t>
+          <t>PAC</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -3797,19 +3797,19 @@
         <v>8</v>
       </c>
       <c r="G47" t="n">
-        <v>6.9</v>
+        <v>7.4</v>
       </c>
       <c r="H47" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="I47" t="n">
-        <v>1.16</v>
+        <v>1.24</v>
       </c>
       <c r="J47" t="n">
         <v>33</v>
       </c>
       <c r="K47" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L47" t="n">
         <v>2</v>
@@ -3818,12 +3818,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Boaster</t>
+          <t>purp0</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>FNATIC</t>
+          <t>Team Liquid</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3833,32 +3833,32 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>I</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="F48" t="n">
         <v>8</v>
       </c>
       <c r="G48" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="H48" s="4" t="n">
-        <v>2.3</v>
+        <v>6.9</v>
+      </c>
+      <c r="H48" t="n">
+        <v>1.1</v>
       </c>
       <c r="I48" t="n">
-        <v>0.97</v>
+        <v>1.16</v>
       </c>
       <c r="J48" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="K48" t="n">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="L48" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49">
@@ -3956,12 +3956,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>nAts</t>
+          <t>Chronicle</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Team Liquid</t>
+          <t>Team Vitality</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3975,25 +3975,25 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="F51" t="n">
         <v>7</v>
       </c>
       <c r="G51" t="n">
-        <v>7.8</v>
+        <v>8.9</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.8</v>
+        <v>-1.9</v>
       </c>
       <c r="I51" t="n">
-        <v>1.13</v>
+        <v>0.77</v>
       </c>
       <c r="J51" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="K51" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L51" t="n">
         <v>2</v>
@@ -4002,58 +4002,58 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Xross</t>
+          <t>nAts</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Nongshim RedForce</t>
+          <t>Team Liquid</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>PAC</t>
+          <t>EMEA</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F52" t="n">
         <v>7</v>
       </c>
       <c r="G52" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="H52" s="3" t="n">
-        <v>-2.5</v>
+        <v>7.8</v>
+      </c>
+      <c r="H52" t="n">
+        <v>-0.8</v>
       </c>
       <c r="I52" t="n">
-        <v>0.93</v>
+        <v>1.13</v>
       </c>
       <c r="J52" t="n">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="K52" t="n">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="L52" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>eko</t>
+          <t>Xross</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>ZETA DIVISION</t>
+          <t>Nongshim RedForce</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -4063,26 +4063,26 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>I</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>8.5</v>
+        <v>10</v>
       </c>
       <c r="F53" t="n">
         <v>7</v>
       </c>
       <c r="G53" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="H53" t="n">
-        <v>1.8</v>
+        <v>9.5</v>
+      </c>
+      <c r="H53" s="3" t="n">
+        <v>-2.5</v>
       </c>
       <c r="I53" t="n">
-        <v>0.83</v>
+        <v>0.93</v>
       </c>
       <c r="J53" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="K53" t="n">
         <v>51</v>
@@ -4094,136 +4094,136 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Crewen</t>
+          <t>eko</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>BBL Esports</t>
+          <t>ZETA DIVISION</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>EMEA</t>
+          <t>PAC</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="F54" t="n">
         <v>7</v>
       </c>
       <c r="G54" t="n">
-        <v>8.199999999999999</v>
+        <v>5.2</v>
       </c>
       <c r="H54" t="n">
-        <v>-1.2</v>
+        <v>1.8</v>
       </c>
       <c r="I54" t="n">
-        <v>0.98</v>
+        <v>0.83</v>
       </c>
       <c r="J54" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="K54" t="n">
-        <v>28</v>
+        <v>51</v>
       </c>
       <c r="L54" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>SugarZ3ro</t>
+          <t>Crewen</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ZETA DIVISION</t>
+          <t>BBL Esports</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>PAC</t>
+          <t>EMEA</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="F55" t="n">
         <v>7</v>
       </c>
       <c r="G55" t="n">
-        <v>6.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H55" t="n">
-        <v>0.8</v>
+        <v>-1.2</v>
       </c>
       <c r="I55" t="n">
-        <v>0.95</v>
+        <v>0.98</v>
       </c>
       <c r="J55" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="K55" t="n">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="L55" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>echo</t>
+          <t>SugarZ3ro</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Eternal Fire</t>
+          <t>ZETA DIVISION</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>EMEA</t>
+          <t>PAC</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="F56" t="n">
         <v>7</v>
       </c>
       <c r="G56" t="n">
-        <v>6.5</v>
+        <v>6.2</v>
       </c>
       <c r="H56" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="I56" t="n">
-        <v>1.06</v>
+        <v>0.95</v>
       </c>
       <c r="J56" t="n">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="K56" t="n">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="L56" t="n">
         <v>3</v>
@@ -4232,12 +4232,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Krostaly</t>
+          <t>echo</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>FUT Esports</t>
+          <t>Eternal Fire</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -4247,7 +4247,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E57" t="n">
@@ -4257,19 +4257,19 @@
         <v>7</v>
       </c>
       <c r="G57" t="n">
-        <v>7.4</v>
+        <v>6.5</v>
       </c>
       <c r="H57" t="n">
-        <v>-0.4</v>
+        <v>0.5</v>
       </c>
       <c r="I57" t="n">
-        <v>0.79</v>
+        <v>1.06</v>
       </c>
       <c r="J57" t="n">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="K57" t="n">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="L57" t="n">
         <v>3</v>
@@ -4278,58 +4278,58 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Meiy</t>
+          <t>Krostaly</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Detonation FocusMe</t>
+          <t>FUT Esports</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>PAC</t>
+          <t>EMEA</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>I</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="F58" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G58" t="n">
-        <v>7.7</v>
+        <v>7.4</v>
       </c>
       <c r="H58" t="n">
-        <v>-1.7</v>
+        <v>-0.4</v>
       </c>
       <c r="I58" t="n">
-        <v>1.06</v>
+        <v>0.79</v>
       </c>
       <c r="J58" t="n">
         <v>36</v>
       </c>
       <c r="K58" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="L58" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Francis</t>
+          <t>Meiy</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Nongshim RedForce</t>
+          <t>Detonation FocusMe</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -4343,74 +4343,74 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F59" t="n">
         <v>6</v>
       </c>
       <c r="G59" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="H59" s="3" t="n">
-        <v>-3.1</v>
+        <v>7.7</v>
+      </c>
+      <c r="H59" t="n">
+        <v>-1.7</v>
       </c>
       <c r="I59" t="n">
-        <v>0.86</v>
+        <v>1.06</v>
       </c>
       <c r="J59" t="n">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="K59" t="n">
-        <v>57</v>
+        <v>31</v>
       </c>
       <c r="L59" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Chronicle</t>
+          <t>Francis</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Team Vitality</t>
+          <t>Nongshim RedForce</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>EMEA</t>
+          <t>PAC</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="F60" t="n">
         <v>6</v>
       </c>
       <c r="G60" t="n">
-        <v>8.9</v>
+        <v>9.1</v>
       </c>
       <c r="H60" s="3" t="n">
-        <v>-2.9</v>
+        <v>-3.1</v>
       </c>
       <c r="I60" t="n">
-        <v>0.77</v>
+        <v>0.86</v>
       </c>
       <c r="J60" t="n">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="K60" t="n">
-        <v>24</v>
+        <v>57</v>
       </c>
       <c r="L60" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="61">
@@ -7400,17 +7400,17 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>OUT: Marteen</t>
+          <t>OUT: Xross</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>IN: Jemkin</t>
+          <t>IN: Killua</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>Slot: W</t>
+          <t>Slot: I</t>
         </is>
       </c>
     </row>
@@ -7444,17 +7444,17 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>OUT: Xross</t>
+          <t>OUT: Marteen</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>IN: Killua</t>
+          <t>IN: Jemkin</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>Slot: I</t>
+          <t>Slot: W</t>
         </is>
       </c>
     </row>
@@ -7700,12 +7700,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Udotan</t>
+          <t>Free1ng</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Global Esports</t>
+          <t>DRX</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -7714,13 +7714,13 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>9</v>
+        <v>7.5</v>
       </c>
       <c r="F27" t="n">
-        <v>10.4</v>
+        <v>8.1</v>
       </c>
       <c r="G27" t="n">
-        <v>10.4</v>
+        <v>8.1</v>
       </c>
       <c r="H27" t="inlineStr"/>
     </row>
@@ -7732,12 +7732,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Free1ng</t>
+          <t>Udotan</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>DRX</t>
+          <t>Global Esports</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -7746,13 +7746,13 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>7.5</v>
+        <v>9</v>
       </c>
       <c r="F28" t="n">
-        <v>8.1</v>
+        <v>10.4</v>
       </c>
       <c r="G28" t="n">
-        <v>8.1</v>
+        <v>10.4</v>
       </c>
       <c r="H28" t="inlineStr"/>
     </row>
@@ -7884,7 +7884,7 @@
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>OUT: Krostaly</t>
+          <t>OUT: Lovers rock</t>
         </is>
       </c>
       <c r="C35" s="7" t="inlineStr">
@@ -7906,17 +7906,17 @@
       </c>
       <c r="B36" s="7" t="inlineStr">
         <is>
-          <t>OUT: Jemkin</t>
+          <t>OUT: Stax</t>
         </is>
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>IN: Veqaj</t>
+          <t>IN: Sayonara</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>Slot: W</t>
+          <t>Slot: I</t>
         </is>
       </c>
     </row>
@@ -7928,12 +7928,12 @@
       </c>
       <c r="B37" s="7" t="inlineStr">
         <is>
-          <t>OUT: Lovers rock</t>
+          <t>OUT: Jemkin</t>
         </is>
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
-          <t>IN: skuba</t>
+          <t>IN: Veqaj</t>
         </is>
       </c>
       <c r="D37" s="7" t="inlineStr">
@@ -8092,27 +8092,27 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Stax</t>
+          <t>Sayonara</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>Team Vitality</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>PAC</t>
+          <t>EMEA</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F42" t="n">
-        <v>6.8</v>
+        <v>10.3</v>
       </c>
       <c r="G42" t="n">
-        <v>6.8</v>
+        <v>10.3</v>
       </c>
       <c r="H42" t="inlineStr"/>
     </row>
@@ -8188,12 +8188,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Udotan</t>
+          <t>Free1ng</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Global Esports</t>
+          <t>DRX</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -8202,7 +8202,7 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>9</v>
+        <v>7.5</v>
       </c>
       <c r="F45" t="n">
         <v>9.4</v>
@@ -8220,12 +8220,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Free1ng</t>
+          <t>Udotan</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>DRX</t>
+          <t>Global Esports</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -8234,7 +8234,7 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>7.5</v>
+        <v>9</v>
       </c>
       <c r="F46" t="n">
         <v>9.4</v>
@@ -8269,10 +8269,10 @@
         <v>10.5</v>
       </c>
       <c r="F47" t="n">
-        <v>11</v>
+        <v>11.3</v>
       </c>
       <c r="G47" t="n">
-        <v>11</v>
+        <v>11.3</v>
       </c>
       <c r="H47" t="inlineStr"/>
     </row>
@@ -8284,27 +8284,27 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>skuba</t>
+          <t>seven</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>NRG Esports</t>
+          <t>PCIFIC Esports</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>AMER</t>
+          <t>EMEA</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="F48" t="n">
-        <v>9.699999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="G48" t="n">
-        <v>9.699999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="H48" t="inlineStr"/>
     </row>
@@ -8316,12 +8316,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>seven</t>
+          <t>Krostaly</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>PCIFIC Esports</t>
+          <t>FUT Esports</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8330,13 +8330,13 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F49" t="n">
-        <v>7.4</v>
+        <v>6.3</v>
       </c>
       <c r="G49" t="n">
-        <v>7.4</v>
+        <v>6.3</v>
       </c>
       <c r="H49" t="inlineStr"/>
     </row>
@@ -8347,10 +8347,10 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100</v>
+        <v>99.5</v>
       </c>
       <c r="G50" t="n">
-        <v>117.5</v>
+        <v>118</v>
       </c>
     </row>
     <row r="52">
@@ -8368,7 +8368,7 @@
       </c>
       <c r="B53" s="7" t="inlineStr">
         <is>
-          <t>OUT: Stax</t>
+          <t>OUT: Primmie</t>
         </is>
       </c>
       <c r="C53" s="7" t="inlineStr">
@@ -8395,12 +8395,12 @@
       </c>
       <c r="C54" s="7" t="inlineStr">
         <is>
-          <t>IN: ethan</t>
+          <t>IN: v1c</t>
         </is>
       </c>
       <c r="D54" s="7" t="inlineStr">
         <is>
-          <t>Slot: I</t>
+          <t>Slot: C</t>
         </is>
       </c>
     </row>
@@ -8412,17 +8412,17 @@
       </c>
       <c r="B55" s="7" t="inlineStr">
         <is>
-          <t>OUT: Primmie</t>
+          <t>OUT: Krostaly</t>
         </is>
       </c>
       <c r="C55" s="7" t="inlineStr">
         <is>
-          <t>IN: v1c</t>
+          <t>IN: ethan</t>
         </is>
       </c>
       <c r="D55" s="7" t="inlineStr">
         <is>
-          <t>Slot: C</t>
+          <t>Slot: W</t>
         </is>
       </c>
     </row>
@@ -8576,27 +8576,27 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>ethan</t>
+          <t>Sayonara</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>NRG Esports</t>
+          <t>Team Vitality</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>AMER</t>
+          <t>EMEA</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F60" t="n">
-        <v>8</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="G60" t="n">
-        <v>8</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="H60" t="inlineStr"/>
     </row>
@@ -8672,12 +8672,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Udotan</t>
+          <t>Free1ng</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Global Esports</t>
+          <t>DRX</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8686,13 +8686,13 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>9</v>
+        <v>7.5</v>
       </c>
       <c r="F63" t="n">
-        <v>9.199999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="G63" t="n">
-        <v>9.199999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H63" t="inlineStr"/>
     </row>
@@ -8704,12 +8704,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Free1ng</t>
+          <t>Udotan</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>DRX</t>
+          <t>Global Esports</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8718,13 +8718,13 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>7.5</v>
+        <v>9</v>
       </c>
       <c r="F64" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="G64" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="H64" t="inlineStr"/>
     </row>
@@ -8753,10 +8753,10 @@
         <v>10.5</v>
       </c>
       <c r="F65" t="n">
-        <v>9.699999999999999</v>
+        <v>9.9</v>
       </c>
       <c r="G65" t="n">
-        <v>9.699999999999999</v>
+        <v>9.9</v>
       </c>
       <c r="H65" t="inlineStr"/>
     </row>
@@ -8768,27 +8768,27 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>skuba</t>
+          <t>seven</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>NRG Esports</t>
+          <t>PCIFIC Esports</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>AMER</t>
+          <t>EMEA</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="F66" t="n">
-        <v>9.300000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="G66" t="n">
-        <v>9.300000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="H66" t="inlineStr"/>
     </row>
@@ -8800,27 +8800,27 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>seven</t>
+          <t>ethan</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>PCIFIC Esports</t>
+          <t>NRG Esports</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>EMEA</t>
+          <t>AMER</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F67" t="n">
-        <v>8.699999999999999</v>
+        <v>8</v>
       </c>
       <c r="G67" t="n">
-        <v>8.699999999999999</v>
+        <v>8</v>
       </c>
       <c r="H67" t="inlineStr"/>
     </row>
@@ -8831,10 +8831,10 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>99.5</v>
+        <v>100</v>
       </c>
       <c r="G68" t="n">
-        <v>110</v>
+        <v>110.2</v>
       </c>
     </row>
     <row r="70">
@@ -8852,17 +8852,17 @@
       </c>
       <c r="B71" s="7" t="inlineStr">
         <is>
-          <t>OUT: Veqaj</t>
+          <t>OUT: xavi8k</t>
         </is>
       </c>
       <c r="C71" s="7" t="inlineStr">
         <is>
-          <t>IN: Cryocells</t>
+          <t>IN: JohnQT</t>
         </is>
       </c>
       <c r="D71" s="7" t="inlineStr">
         <is>
-          <t>Slot: W</t>
+          <t>Slot: C</t>
         </is>
       </c>
     </row>
@@ -8874,17 +8874,17 @@
       </c>
       <c r="B72" s="7" t="inlineStr">
         <is>
-          <t>OUT: seven</t>
+          <t>OUT: Veqaj</t>
         </is>
       </c>
       <c r="C72" s="7" t="inlineStr">
         <is>
-          <t>IN: JohnQT</t>
+          <t>IN: cauanzin</t>
         </is>
       </c>
       <c r="D72" s="7" t="inlineStr">
         <is>
-          <t>Slot: C</t>
+          <t>Slot: W</t>
         </is>
       </c>
     </row>
@@ -8896,12 +8896,12 @@
       </c>
       <c r="B73" s="7" t="inlineStr">
         <is>
-          <t>OUT: xavi8k</t>
+          <t>OUT: seven</t>
         </is>
       </c>
       <c r="C73" s="7" t="inlineStr">
         <is>
-          <t>IN: cauanzin</t>
+          <t>IN: skuba</t>
         </is>
       </c>
       <c r="D73" s="7" t="inlineStr">
@@ -9060,27 +9060,27 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>ethan</t>
+          <t>Sayonara</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>NRG Esports</t>
+          <t>Team Vitality</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>AMER</t>
+          <t>EMEA</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F78" t="n">
-        <v>8.199999999999999</v>
+        <v>11.2</v>
       </c>
       <c r="G78" t="n">
-        <v>8.199999999999999</v>
+        <v>11.2</v>
       </c>
       <c r="H78" t="inlineStr"/>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>JohnQT</t>
+          <t>v1c</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Sentinels</t>
+          <t>Cloud9</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9106,13 +9106,13 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F79" t="n">
-        <v>8.9</v>
+        <v>8.6</v>
       </c>
       <c r="G79" t="n">
-        <v>8.9</v>
+        <v>8.6</v>
       </c>
       <c r="H79" t="inlineStr"/>
     </row>
@@ -9124,12 +9124,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>v1c</t>
+          <t>JohnQT</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Cloud9</t>
+          <t>Sentinels</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9138,13 +9138,13 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F80" t="n">
-        <v>8.6</v>
+        <v>8.9</v>
       </c>
       <c r="G80" t="n">
-        <v>8.6</v>
+        <v>8.9</v>
       </c>
       <c r="H80" t="inlineStr"/>
     </row>
@@ -9156,12 +9156,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Udotan</t>
+          <t>Free1ng</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Global Esports</t>
+          <t>DRX</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -9170,13 +9170,13 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>9</v>
+        <v>7.5</v>
       </c>
       <c r="F81" t="n">
-        <v>9.300000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="G81" t="n">
-        <v>9.300000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="H81" t="inlineStr"/>
     </row>
@@ -9188,12 +9188,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Free1ng</t>
+          <t>Udotan</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>DRX</t>
+          <t>Global Esports</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -9202,13 +9202,13 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>7.5</v>
+        <v>9</v>
       </c>
       <c r="F82" t="n">
-        <v>8.1</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="G82" t="n">
-        <v>8.1</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="H82" t="inlineStr"/>
     </row>
@@ -9220,12 +9220,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Cryocells</t>
+          <t>cauanzin</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>100 Thieves</t>
+          <t>LOUD</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -9234,13 +9234,13 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>10.5</v>
+        <v>6</v>
       </c>
       <c r="F83" t="n">
-        <v>8.699999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="G83" t="n">
-        <v>8.699999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="H83" t="inlineStr"/>
     </row>
@@ -9284,12 +9284,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>cauanzin</t>
+          <t>ethan</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>LOUD</t>
+          <t>NRG Esports</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -9298,13 +9298,13 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F85" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="G85" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H85" t="inlineStr"/>
     </row>
@@ -9315,10 +9315,10 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100</v>
+        <v>99.5</v>
       </c>
       <c r="G86" t="n">
-        <v>107.8</v>
+        <v>110.4</v>
       </c>
     </row>
     <row r="88">
@@ -9336,7 +9336,7 @@
       </c>
       <c r="B89" s="7" t="inlineStr">
         <is>
-          <t>OUT: Killua</t>
+          <t>OUT: BuZz</t>
         </is>
       </c>
       <c r="C89" s="7" t="inlineStr">
@@ -9358,7 +9358,7 @@
       </c>
       <c r="B90" s="7" t="inlineStr">
         <is>
-          <t>OUT: BuZz</t>
+          <t>OUT: Sayonara</t>
         </is>
       </c>
       <c r="C90" s="7" t="inlineStr">
@@ -9385,7 +9385,7 @@
       </c>
       <c r="C91" s="7" t="inlineStr">
         <is>
-          <t>IN: Bao</t>
+          <t>IN: Tex</t>
         </is>
       </c>
       <c r="D91" s="7" t="inlineStr">
@@ -9444,12 +9444,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>aspas</t>
+          <t>koalanoob</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>MIBR</t>
+          <t>FURIA</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -9458,19 +9458,15 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="F93" t="n">
-        <v>11.5</v>
+        <v>10.2</v>
       </c>
       <c r="G93" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>IGL</t>
-        </is>
-      </c>
+        <v>10.2</v>
+      </c>
+      <c r="H93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -9480,12 +9476,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>koalanoob</t>
+          <t>aspas</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>FURIA</t>
+          <t>MIBR</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -9494,15 +9490,19 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="F94" t="n">
-        <v>10.2</v>
+        <v>11.5</v>
       </c>
       <c r="G94" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="H94" t="inlineStr"/>
+        <v>23.1</v>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>IGL</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -9512,27 +9512,27 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>ethan</t>
+          <t>Killua</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>NRG Esports</t>
+          <t>FULL SENSE</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>AMER</t>
+          <t>PAC</t>
         </is>
       </c>
       <c r="E95" t="n">
         <v>8</v>
       </c>
       <c r="F95" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="G95" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="H95" t="inlineStr"/>
     </row>
@@ -9576,12 +9576,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>JohnQT</t>
+          <t>v1c</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Sentinels</t>
+          <t>Cloud9</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -9590,13 +9590,13 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F97" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="G97" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="H97" t="inlineStr"/>
     </row>
@@ -9608,12 +9608,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>v1c</t>
+          <t>JohnQT</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Cloud9</t>
+          <t>Sentinels</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -9622,13 +9622,13 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F98" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="G98" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="H98" t="inlineStr"/>
     </row>
@@ -9672,12 +9672,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Bao</t>
+          <t>Tex</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Evil Geniuses</t>
+          <t>MIBR</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -9686,13 +9686,13 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="F100" t="n">
-        <v>6.7</v>
+        <v>8.1</v>
       </c>
       <c r="G100" t="n">
-        <v>6.7</v>
+        <v>8.1</v>
       </c>
       <c r="H100" t="inlineStr"/>
     </row>
@@ -9704,12 +9704,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Cryocells</t>
+          <t>cauanzin</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>100 Thieves</t>
+          <t>LOUD</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -9718,13 +9718,13 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>10.5</v>
+        <v>6</v>
       </c>
       <c r="F101" t="n">
-        <v>9.300000000000001</v>
+        <v>7.1</v>
       </c>
       <c r="G101" t="n">
-        <v>9.300000000000001</v>
+        <v>7.1</v>
       </c>
       <c r="H101" t="inlineStr"/>
     </row>
@@ -9768,12 +9768,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>cauanzin</t>
+          <t>ethan</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>LOUD</t>
+          <t>NRG Esports</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -9782,13 +9782,13 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F103" t="n">
-        <v>7.1</v>
+        <v>7.7</v>
       </c>
       <c r="G103" t="n">
-        <v>7.1</v>
+        <v>7.7</v>
       </c>
       <c r="H103" t="inlineStr"/>
     </row>
@@ -9799,10 +9799,10 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>99.5</v>
+        <v>98.5</v>
       </c>
       <c r="G104" t="n">
-        <v>95.90000000000001</v>
+        <v>87.90000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -10262,17 +10262,17 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>OUT: Munchkin</t>
+          <t>OUT: xeus</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>IN: Patmen</t>
+          <t>IN: Eggsterr</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>Slot: C</t>
+          <t>Slot: D1</t>
         </is>
       </c>
     </row>
@@ -10284,17 +10284,17 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>OUT: xeus</t>
+          <t>OUT: PROFEK</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>IN: Udotan</t>
+          <t>IN: Patmen</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>Slot: W</t>
+          <t>Slot: C2</t>
         </is>
       </c>
     </row>
@@ -10306,17 +10306,17 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>OUT: PROFEK</t>
+          <t>OUT: Munchkin</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>IN: Eggsterr</t>
+          <t>IN: Udotan</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>Slot: D</t>
+          <t>Slot: W2</t>
         </is>
       </c>
     </row>
@@ -10365,71 +10365,71 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D1</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Lar0k</t>
+          <t>Eggsterr</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>BBL Esports</t>
+          <t>ENVY</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>EMEA</t>
+          <t>AMER</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>12</v>
+        <v>7.5</v>
       </c>
       <c r="F21" t="n">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="G21" t="n">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Eggsterr</t>
+          <t>Lar0k</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ENVY</t>
+          <t>BBL Esports</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>AMER</t>
+          <t>EMEA</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>7.5</v>
+        <v>12</v>
       </c>
       <c r="F22" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="G22" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>I1</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10461,7 +10461,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>I2</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10493,7 +10493,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C1</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -10515,17 +10515,17 @@
         <v>10.5</v>
       </c>
       <c r="F25" t="n">
-        <v>9.1</v>
+        <v>9.4</v>
       </c>
       <c r="G25" t="n">
-        <v>9.1</v>
+        <v>9.4</v>
       </c>
       <c r="H25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -10557,7 +10557,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -10589,7 +10589,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -10621,7 +10621,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>W1</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -10657,7 +10657,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>W2</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -10689,7 +10689,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>W3</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -10728,7 +10728,7 @@
         <v>100</v>
       </c>
       <c r="G32" t="n">
-        <v>111.6</v>
+        <v>111.9</v>
       </c>
     </row>
     <row r="34">
@@ -10746,7 +10746,7 @@
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>OUT: Kushy</t>
+          <t>OUT: Lar0k</t>
         </is>
       </c>
       <c r="C35" s="7" t="inlineStr">
@@ -10756,7 +10756,7 @@
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>Slot: D</t>
+          <t>Slot: D2</t>
         </is>
       </c>
     </row>
@@ -10768,7 +10768,7 @@
       </c>
       <c r="B36" s="7" t="inlineStr">
         <is>
-          <t>OUT: Lar0k</t>
+          <t>OUT: Kushy</t>
         </is>
       </c>
       <c r="C36" s="7" t="inlineStr">
@@ -10778,7 +10778,7 @@
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>Slot: I</t>
+          <t>Slot: I1</t>
         </is>
       </c>
     </row>
@@ -10800,7 +10800,7 @@
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>Slot: S</t>
+          <t>Slot: S2</t>
         </is>
       </c>
     </row>
@@ -10849,75 +10849,75 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D1</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Primmie</t>
+          <t>Eggsterr</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>FULL SENSE</t>
+          <t>ENVY</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>PAC</t>
+          <t>AMER</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>13.5</v>
+        <v>7.5</v>
       </c>
       <c r="F39" t="n">
-        <v>13.4</v>
+        <v>7.5</v>
       </c>
       <c r="G39" t="n">
-        <v>26.7</v>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>IGL</t>
-        </is>
-      </c>
+        <v>7.5</v>
+      </c>
+      <c r="H39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Eggsterr</t>
+          <t>Primmie</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>ENVY</t>
+          <t>FULL SENSE</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>AMER</t>
+          <t>PAC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>7.5</v>
+        <v>13.5</v>
       </c>
       <c r="F40" t="n">
-        <v>7.5</v>
+        <v>13.4</v>
       </c>
       <c r="G40" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="H40" t="inlineStr"/>
+        <v>26.7</v>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>IGL</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>I1</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -10949,7 +10949,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>I2</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -10981,7 +10981,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C1</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -11003,17 +11003,17 @@
         <v>10.5</v>
       </c>
       <c r="F43" t="n">
-        <v>11</v>
+        <v>11.3</v>
       </c>
       <c r="G43" t="n">
-        <v>11</v>
+        <v>11.3</v>
       </c>
       <c r="H43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -11045,7 +11045,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -11077,7 +11077,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -11109,7 +11109,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>W1</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -11141,7 +11141,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>W2</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -11173,7 +11173,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>W3</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -11212,7 +11212,7 @@
         <v>100</v>
       </c>
       <c r="G50" t="n">
-        <v>118.6</v>
+        <v>118.9</v>
       </c>
     </row>
     <row r="52">
@@ -11230,17 +11230,17 @@
       </c>
       <c r="B53" s="7" t="inlineStr">
         <is>
-          <t>OUT: BeYN</t>
+          <t>OUT: Jemkin</t>
         </is>
       </c>
       <c r="C53" s="7" t="inlineStr">
         <is>
-          <t>IN: koalanoob</t>
+          <t>IN: skuba</t>
         </is>
       </c>
       <c r="D53" s="7" t="inlineStr">
         <is>
-          <t>Slot: W</t>
+          <t>Slot: W1</t>
         </is>
       </c>
     </row>
@@ -11252,17 +11252,17 @@
       </c>
       <c r="B54" s="7" t="inlineStr">
         <is>
-          <t>OUT: Jemkin</t>
+          <t>OUT: Udotan</t>
         </is>
       </c>
       <c r="C54" s="7" t="inlineStr">
         <is>
-          <t>IN: skuba</t>
+          <t>IN: koalanoob</t>
         </is>
       </c>
       <c r="D54" s="7" t="inlineStr">
         <is>
-          <t>Slot: W</t>
+          <t>Slot: W2</t>
         </is>
       </c>
     </row>
@@ -11274,7 +11274,7 @@
       </c>
       <c r="B55" s="7" t="inlineStr">
         <is>
-          <t>OUT: Udotan</t>
+          <t>OUT: BeYN</t>
         </is>
       </c>
       <c r="C55" s="7" t="inlineStr">
@@ -11284,7 +11284,7 @@
       </c>
       <c r="D55" s="7" t="inlineStr">
         <is>
-          <t>Slot: W</t>
+          <t>Slot: W3</t>
         </is>
       </c>
     </row>
@@ -11333,71 +11333,71 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D1</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Primmie</t>
+          <t>Eggsterr</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>FULL SENSE</t>
+          <t>ENVY</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>PAC</t>
+          <t>AMER</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>13.5</v>
+        <v>7.5</v>
       </c>
       <c r="F57" t="n">
-        <v>11.1</v>
+        <v>7.4</v>
       </c>
       <c r="G57" t="n">
-        <v>11.1</v>
+        <v>7.4</v>
       </c>
       <c r="H57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Eggsterr</t>
+          <t>Primmie</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>ENVY</t>
+          <t>FULL SENSE</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>AMER</t>
+          <t>PAC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>7.5</v>
+        <v>13.5</v>
       </c>
       <c r="F58" t="n">
-        <v>7.4</v>
+        <v>11.1</v>
       </c>
       <c r="G58" t="n">
-        <v>7.4</v>
+        <v>11.1</v>
       </c>
       <c r="H58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>I1</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -11429,7 +11429,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>I2</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -11461,7 +11461,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C1</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -11483,17 +11483,17 @@
         <v>10.5</v>
       </c>
       <c r="F61" t="n">
-        <v>9.699999999999999</v>
+        <v>9.9</v>
       </c>
       <c r="G61" t="n">
-        <v>9.699999999999999</v>
+        <v>9.9</v>
       </c>
       <c r="H61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -11525,7 +11525,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -11557,7 +11557,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -11589,17 +11589,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>W1</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>koalanoob</t>
+          <t>skuba</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>FURIA</t>
+          <t>NRG Esports</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -11608,34 +11608,30 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>12.5</v>
+        <v>9.5</v>
       </c>
       <c r="F65" t="n">
-        <v>10.6</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="G65" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>IGL</t>
-        </is>
-      </c>
+        <v>9.300000000000001</v>
+      </c>
+      <c r="H65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>W2</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>skuba</t>
+          <t>koalanoob</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>NRG Esports</t>
+          <t>FURIA</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -11644,20 +11640,24 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>9.5</v>
+        <v>12.5</v>
       </c>
       <c r="F66" t="n">
-        <v>9.300000000000001</v>
+        <v>10.6</v>
       </c>
       <c r="G66" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="H66" t="inlineStr"/>
+        <v>21.1</v>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>IGL</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>W3</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -11696,7 +11696,7 @@
         <v>100</v>
       </c>
       <c r="G68" t="n">
-        <v>108</v>
+        <v>108.3</v>
       </c>
     </row>
     <row r="70">
@@ -11719,12 +11719,12 @@
       </c>
       <c r="C71" s="7" t="inlineStr">
         <is>
-          <t>IN: Keiko</t>
+          <t>IN: cauanzin</t>
         </is>
       </c>
       <c r="D71" s="7" t="inlineStr">
         <is>
-          <t>Slot: C</t>
+          <t>Slot: I2</t>
         </is>
       </c>
     </row>
@@ -11736,7 +11736,7 @@
       </c>
       <c r="B72" s="7" t="inlineStr">
         <is>
-          <t>OUT: Patmen</t>
+          <t>OUT: Veqaj</t>
         </is>
       </c>
       <c r="C72" s="7" t="inlineStr">
@@ -11746,7 +11746,7 @@
       </c>
       <c r="D72" s="7" t="inlineStr">
         <is>
-          <t>Slot: C</t>
+          <t>Slot: C1</t>
         </is>
       </c>
     </row>
@@ -11758,17 +11758,17 @@
       </c>
       <c r="B73" s="7" t="inlineStr">
         <is>
-          <t>OUT: Veqaj</t>
+          <t>OUT: Patmen</t>
         </is>
       </c>
       <c r="C73" s="7" t="inlineStr">
         <is>
-          <t>IN: cauanzin</t>
+          <t>IN: Keiko</t>
         </is>
       </c>
       <c r="D73" s="7" t="inlineStr">
         <is>
-          <t>Slot: I</t>
+          <t>Slot: C2</t>
         </is>
       </c>
     </row>
@@ -11817,71 +11817,71 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D1</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Primmie</t>
+          <t>Eggsterr</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>FULL SENSE</t>
+          <t>ENVY</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>PAC</t>
+          <t>AMER</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>13.5</v>
+        <v>7.5</v>
       </c>
       <c r="F75" t="n">
-        <v>11</v>
+        <v>6.9</v>
       </c>
       <c r="G75" t="n">
-        <v>11</v>
+        <v>6.9</v>
       </c>
       <c r="H75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Eggsterr</t>
+          <t>Primmie</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>ENVY</t>
+          <t>FULL SENSE</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>AMER</t>
+          <t>PAC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>7.5</v>
+        <v>13.5</v>
       </c>
       <c r="F76" t="n">
-        <v>6.9</v>
+        <v>11</v>
       </c>
       <c r="G76" t="n">
-        <v>6.9</v>
+        <v>11</v>
       </c>
       <c r="H76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>I1</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -11913,7 +11913,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>I2</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -11945,17 +11945,17 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C1</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Keiko</t>
+          <t>JohnQT</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>NRG Esports</t>
+          <t>Sentinels</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -11964,34 +11964,30 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>12.5</v>
+        <v>9</v>
       </c>
       <c r="F79" t="n">
-        <v>10.2</v>
+        <v>8.9</v>
       </c>
       <c r="G79" t="n">
-        <v>20.3</v>
-      </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>IGL</t>
-        </is>
-      </c>
+        <v>8.9</v>
+      </c>
+      <c r="H79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>JohnQT</t>
+          <t>Keiko</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Sentinels</t>
+          <t>NRG Esports</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -12000,20 +11996,24 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>9</v>
+        <v>12.5</v>
       </c>
       <c r="F80" t="n">
-        <v>8.9</v>
+        <v>10.2</v>
       </c>
       <c r="G80" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="H80" t="inlineStr"/>
+        <v>20.3</v>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>IGL</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -12045,7 +12045,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -12077,17 +12077,17 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>W1</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>koalanoob</t>
+          <t>skuba</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>FURIA</t>
+          <t>NRG Esports</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -12096,30 +12096,30 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>12.5</v>
+        <v>9.5</v>
       </c>
       <c r="F83" t="n">
-        <v>9.9</v>
+        <v>9.6</v>
       </c>
       <c r="G83" t="n">
-        <v>9.9</v>
+        <v>9.6</v>
       </c>
       <c r="H83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>W2</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>skuba</t>
+          <t>koalanoob</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>NRG Esports</t>
+          <t>FURIA</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -12128,20 +12128,20 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>9.5</v>
+        <v>12.5</v>
       </c>
       <c r="F84" t="n">
-        <v>9.6</v>
+        <v>9.9</v>
       </c>
       <c r="G84" t="n">
-        <v>9.6</v>
+        <v>9.9</v>
       </c>
       <c r="H84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>W3</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -12198,7 +12198,7 @@
       </c>
       <c r="B89" s="7" t="inlineStr">
         <is>
-          <t>OUT: Free1ng</t>
+          <t>OUT: Primmie</t>
         </is>
       </c>
       <c r="C89" s="7" t="inlineStr">
@@ -12208,7 +12208,7 @@
       </c>
       <c r="D89" s="7" t="inlineStr">
         <is>
-          <t>Slot: D</t>
+          <t>Slot: D2</t>
         </is>
       </c>
     </row>
@@ -12230,7 +12230,7 @@
       </c>
       <c r="D90" s="7" t="inlineStr">
         <is>
-          <t>Slot: I</t>
+          <t>Slot: I1</t>
         </is>
       </c>
     </row>
@@ -12242,7 +12242,7 @@
       </c>
       <c r="B91" s="7" t="inlineStr">
         <is>
-          <t>OUT: Primmie</t>
+          <t>OUT: Free1ng</t>
         </is>
       </c>
       <c r="C91" s="7" t="inlineStr">
@@ -12252,7 +12252,7 @@
       </c>
       <c r="D91" s="7" t="inlineStr">
         <is>
-          <t>Slot: S</t>
+          <t>Slot: S1</t>
         </is>
       </c>
     </row>
@@ -12301,17 +12301,17 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D1</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>aspas</t>
+          <t>Eggsterr</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>MIBR</t>
+          <t>ENVY</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -12320,34 +12320,30 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>14.5</v>
+        <v>7.5</v>
       </c>
       <c r="F93" t="n">
-        <v>11.5</v>
+        <v>7.7</v>
       </c>
       <c r="G93" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>IGL</t>
-        </is>
-      </c>
+        <v>7.7</v>
+      </c>
+      <c r="H93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Eggsterr</t>
+          <t>aspas</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>ENVY</t>
+          <t>MIBR</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12356,20 +12352,24 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>7.5</v>
+        <v>14.5</v>
       </c>
       <c r="F94" t="n">
-        <v>7.7</v>
+        <v>11.5</v>
       </c>
       <c r="G94" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="H94" t="inlineStr"/>
+        <v>23.1</v>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>IGL</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>I1</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -12401,7 +12401,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>I2</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -12433,17 +12433,17 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C1</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Keiko</t>
+          <t>JohnQT</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>NRG Esports</t>
+          <t>Sentinels</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -12452,30 +12452,30 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>12.5</v>
+        <v>9</v>
       </c>
       <c r="F97" t="n">
-        <v>9.5</v>
+        <v>7.6</v>
       </c>
       <c r="G97" t="n">
-        <v>9.5</v>
+        <v>7.6</v>
       </c>
       <c r="H97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>JohnQT</t>
+          <t>Keiko</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Sentinels</t>
+          <t>NRG Esports</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12484,20 +12484,20 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>9</v>
+        <v>12.5</v>
       </c>
       <c r="F98" t="n">
-        <v>7.6</v>
+        <v>9.5</v>
       </c>
       <c r="G98" t="n">
-        <v>7.6</v>
+        <v>9.5</v>
       </c>
       <c r="H98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -12529,7 +12529,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -12561,17 +12561,17 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>W1</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>koalanoob</t>
+          <t>skuba</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>FURIA</t>
+          <t>NRG Esports</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12580,30 +12580,30 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>12.5</v>
+        <v>9.5</v>
       </c>
       <c r="F101" t="n">
-        <v>10.2</v>
+        <v>9</v>
       </c>
       <c r="G101" t="n">
-        <v>10.2</v>
+        <v>9</v>
       </c>
       <c r="H101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>W2</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>skuba</t>
+          <t>koalanoob</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>NRG Esports</t>
+          <t>FURIA</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12612,20 +12612,20 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>9.5</v>
+        <v>12.5</v>
       </c>
       <c r="F102" t="n">
-        <v>9</v>
+        <v>10.2</v>
       </c>
       <c r="G102" t="n">
-        <v>9</v>
+        <v>10.2</v>
       </c>
       <c r="H102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>W3</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -13124,7 +13124,7 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>OUT: Jemkin</t>
+          <t>OUT: Lar0k</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
@@ -13134,7 +13134,7 @@
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>Slot: D</t>
+          <t>Slot: D2</t>
         </is>
       </c>
     </row>
@@ -13146,7 +13146,7 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>OUT: Munchkin</t>
+          <t>OUT: Jemkin</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
@@ -13156,7 +13156,7 @@
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>Slot: W</t>
+          <t>Slot: W1</t>
         </is>
       </c>
     </row>
@@ -13168,7 +13168,7 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>OUT: Lar0k</t>
+          <t>OUT: Munchkin</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
@@ -13178,7 +13178,7 @@
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>Slot: W</t>
+          <t>Slot: W2</t>
         </is>
       </c>
     </row>
@@ -13227,17 +13227,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D1</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Derke</t>
+          <t>xeus</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Team Vitality</t>
+          <t>FUT Esports</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -13246,34 +13246,30 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>14</v>
+        <v>10.5</v>
       </c>
       <c r="F21" t="n">
-        <v>11.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="G21" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>IGL</t>
-        </is>
-      </c>
+        <v>9.199999999999999</v>
+      </c>
+      <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>xeus</t>
+          <t>Derke</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>FUT Esports</t>
+          <t>Team Vitality</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -13282,20 +13278,24 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>10.5</v>
+        <v>14</v>
       </c>
       <c r="F22" t="n">
-        <v>9.199999999999999</v>
+        <v>11.9</v>
       </c>
       <c r="G22" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="H22" t="inlineStr"/>
+        <v>23.8</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>IGL</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>I1</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -13327,7 +13327,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>I2</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -13359,7 +13359,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C1</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -13381,17 +13381,17 @@
         <v>10.5</v>
       </c>
       <c r="F25" t="n">
-        <v>9.199999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="G25" t="n">
-        <v>9.199999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="H25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -13413,17 +13413,17 @@
         <v>8.5</v>
       </c>
       <c r="F26" t="n">
-        <v>8.300000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="G26" t="n">
-        <v>8.300000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="H26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -13455,7 +13455,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -13487,7 +13487,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>W1</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -13519,7 +13519,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>W2</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -13551,7 +13551,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>W3</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -13590,7 +13590,7 @@
         <v>100</v>
       </c>
       <c r="G32" t="n">
-        <v>107.6</v>
+        <v>108.9</v>
       </c>
     </row>
     <row r="34">
@@ -13613,12 +13613,12 @@
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>IN: dgzin</t>
+          <t>IN: Killua</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>Slot: D</t>
+          <t>Slot: I1</t>
         </is>
       </c>
     </row>
@@ -13630,17 +13630,17 @@
       </c>
       <c r="B36" s="7" t="inlineStr">
         <is>
-          <t>OUT: xeus</t>
+          <t>OUT: Yetujey</t>
         </is>
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>IN: Killua</t>
+          <t>IN: Bao</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>Slot: I</t>
+          <t>Slot: S2</t>
         </is>
       </c>
     </row>
@@ -13652,7 +13652,7 @@
       </c>
       <c r="B37" s="7" t="inlineStr">
         <is>
-          <t>OUT: PROFEK</t>
+          <t>OUT: BeYN</t>
         </is>
       </c>
       <c r="C37" s="7" t="inlineStr">
@@ -13662,7 +13662,7 @@
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>Slot: C</t>
+          <t>Slot: W3</t>
         </is>
       </c>
     </row>
@@ -13711,17 +13711,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D1</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Derke</t>
+          <t>xeus</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Team Vitality</t>
+          <t>FUT Esports</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -13730,56 +13730,56 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>14</v>
+        <v>10.5</v>
       </c>
       <c r="F39" t="n">
-        <v>11.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="G39" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>IGL</t>
-        </is>
-      </c>
+        <v>9.199999999999999</v>
+      </c>
+      <c r="H39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>dgzin</t>
+          <t>Derke</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Evil Geniuses</t>
+          <t>Team Vitality</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>AMER</t>
+          <t>EMEA</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F40" t="n">
-        <v>10.1</v>
+        <v>11.9</v>
       </c>
       <c r="G40" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="H40" t="inlineStr"/>
+        <v>23.8</v>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>IGL</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>I1</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -13811,7 +13811,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>I2</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -13843,7 +13843,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C1</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -13865,27 +13865,27 @@
         <v>10.5</v>
       </c>
       <c r="F43" t="n">
-        <v>9.199999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="G43" t="n">
-        <v>9.199999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="H43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Dos9</t>
+          <t>PROFEK</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Karmine Corp</t>
+          <t>Team Vitality</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -13894,20 +13894,20 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="F44" t="n">
-        <v>8.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="G44" t="n">
-        <v>8.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="H44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -13939,39 +13939,39 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Yetujey</t>
+          <t>Bao</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>FUT Esports</t>
+          <t>Evil Geniuses</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>EMEA</t>
+          <t>AMER</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="F46" t="n">
-        <v>7.4</v>
+        <v>7.1</v>
       </c>
       <c r="G46" t="n">
-        <v>7.4</v>
+        <v>7.1</v>
       </c>
       <c r="H46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>W1</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -14003,7 +14003,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>W2</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -14035,32 +14035,32 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>W3</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>BeYN</t>
+          <t>Dos9</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>DRX</t>
+          <t>Karmine Corp</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>PAC</t>
+          <t>EMEA</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="F49" t="n">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="G49" t="n">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H49" t="inlineStr"/>
     </row>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100</v>
+        <v>99.5</v>
       </c>
       <c r="G50" t="n">
-        <v>111.8</v>
+        <v>112.7</v>
       </c>
     </row>
     <row r="52">
@@ -14092,17 +14092,17 @@
       </c>
       <c r="B53" s="7" t="inlineStr">
         <is>
-          <t>OUT: BeYN</t>
+          <t>OUT: xeus</t>
         </is>
       </c>
       <c r="C53" s="7" t="inlineStr">
         <is>
-          <t>IN: Cryocells</t>
+          <t>IN: dgzin</t>
         </is>
       </c>
       <c r="D53" s="7" t="inlineStr">
         <is>
-          <t>Slot: S</t>
+          <t>Slot: D1</t>
         </is>
       </c>
     </row>
@@ -14124,7 +14124,7 @@
       </c>
       <c r="D54" s="7" t="inlineStr">
         <is>
-          <t>Slot: W</t>
+          <t>Slot: C1</t>
         </is>
       </c>
     </row>
@@ -14136,17 +14136,17 @@
       </c>
       <c r="B55" s="7" t="inlineStr">
         <is>
-          <t>OUT: Yetujey</t>
+          <t>OUT: Dos9</t>
         </is>
       </c>
       <c r="C55" s="7" t="inlineStr">
         <is>
-          <t>IN: supamen</t>
+          <t>IN: Cryocells</t>
         </is>
       </c>
       <c r="D55" s="7" t="inlineStr">
         <is>
-          <t>Slot: C</t>
+          <t>Slot: W3</t>
         </is>
       </c>
     </row>
@@ -14195,75 +14195,75 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D1</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Derke</t>
+          <t>dgzin</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Team Vitality</t>
+          <t>Evil Geniuses</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>EMEA</t>
+          <t>AMER</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F57" t="n">
-        <v>11.5</v>
+        <v>10.1</v>
       </c>
       <c r="G57" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="H57" t="inlineStr"/>
+        <v>20.3</v>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>IGL</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>dgzin</t>
+          <t>Derke</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Evil Geniuses</t>
+          <t>Team Vitality</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>AMER</t>
+          <t>EMEA</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F58" t="n">
-        <v>10.1</v>
+        <v>11.9</v>
       </c>
       <c r="G58" t="n">
-        <v>20.3</v>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>IGL</t>
-        </is>
-      </c>
+        <v>11.9</v>
+      </c>
+      <c r="H58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>I1</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -14295,7 +14295,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>I2</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -14327,135 +14327,135 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C1</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Dos9</t>
+          <t>v1c</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Karmine Corp</t>
+          <t>Cloud9</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>EMEA</t>
+          <t>AMER</t>
         </is>
       </c>
       <c r="E61" t="n">
         <v>8</v>
       </c>
       <c r="F61" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="G61" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>supamen</t>
+          <t>PROFEK</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Evil Geniuses</t>
+          <t>Team Vitality</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>AMER</t>
+          <t>EMEA</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6.5</v>
+        <v>8.5</v>
       </c>
       <c r="F62" t="n">
-        <v>7.2</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="G62" t="n">
-        <v>7.2</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="H62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Cryocells</t>
+          <t>Free1ng</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>100 Thieves</t>
+          <t>DRX</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>AMER</t>
+          <t>PAC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>10.5</v>
+        <v>7.5</v>
       </c>
       <c r="F63" t="n">
-        <v>9.1</v>
+        <v>8.6</v>
       </c>
       <c r="G63" t="n">
-        <v>9.1</v>
+        <v>8.6</v>
       </c>
       <c r="H63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Free1ng</t>
+          <t>Bao</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>DRX</t>
+          <t>Evil Geniuses</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>PAC</t>
+          <t>AMER</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="F64" t="n">
-        <v>8.6</v>
+        <v>7.1</v>
       </c>
       <c r="G64" t="n">
-        <v>8.6</v>
+        <v>7.1</v>
       </c>
       <c r="H64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>W1</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -14487,7 +14487,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>W2</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -14519,17 +14519,17 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>W3</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>v1c</t>
+          <t>Cryocells</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Cloud9</t>
+          <t>100 Thieves</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -14538,13 +14538,13 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>8</v>
+        <v>10.5</v>
       </c>
       <c r="F67" t="n">
-        <v>8.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="G67" t="n">
-        <v>8.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="H67" t="inlineStr"/>
     </row>
@@ -14555,10 +14555,10 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>99.5</v>
+        <v>100</v>
       </c>
       <c r="G68" t="n">
-        <v>110.7</v>
+        <v>111</v>
       </c>
     </row>
     <row r="70">
@@ -14576,17 +14576,17 @@
       </c>
       <c r="B71" s="7" t="inlineStr">
         <is>
-          <t>OUT: Free1ng</t>
+          <t>OUT: Rosé</t>
         </is>
       </c>
       <c r="C71" s="7" t="inlineStr">
         <is>
-          <t>IN: skuba</t>
+          <t>IN: cauanzin</t>
         </is>
       </c>
       <c r="D71" s="7" t="inlineStr">
         <is>
-          <t>Slot: S</t>
+          <t>Slot: I2</t>
         </is>
       </c>
     </row>
@@ -14598,17 +14598,17 @@
       </c>
       <c r="B72" s="7" t="inlineStr">
         <is>
-          <t>OUT: Killua</t>
+          <t>OUT: PROFEK</t>
         </is>
       </c>
       <c r="C72" s="7" t="inlineStr">
         <is>
-          <t>IN: Xeppaa</t>
+          <t>IN: Erde</t>
         </is>
       </c>
       <c r="D72" s="7" t="inlineStr">
         <is>
-          <t>Slot: I</t>
+          <t>Slot: C2</t>
         </is>
       </c>
     </row>
@@ -14620,17 +14620,17 @@
       </c>
       <c r="B73" s="7" t="inlineStr">
         <is>
-          <t>OUT: Rosé</t>
+          <t>OUT: Free1ng</t>
         </is>
       </c>
       <c r="C73" s="7" t="inlineStr">
         <is>
-          <t>IN: cauanzin</t>
+          <t>IN: skuba</t>
         </is>
       </c>
       <c r="D73" s="7" t="inlineStr">
         <is>
-          <t>Slot: I</t>
+          <t>Slot: S1</t>
         </is>
       </c>
     </row>
@@ -14679,107 +14679,107 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D1</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Derke</t>
+          <t>dgzin</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Team Vitality</t>
+          <t>Evil Geniuses</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>EMEA</t>
+          <t>AMER</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F75" t="n">
-        <v>11.5</v>
+        <v>10.1</v>
       </c>
       <c r="G75" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="H75" t="inlineStr"/>
+        <v>20.3</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>IGL</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>dgzin</t>
+          <t>Derke</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Evil Geniuses</t>
+          <t>Team Vitality</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>AMER</t>
+          <t>EMEA</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F76" t="n">
-        <v>10.1</v>
+        <v>11.9</v>
       </c>
       <c r="G76" t="n">
-        <v>20.3</v>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>IGL</t>
-        </is>
-      </c>
+        <v>11.9</v>
+      </c>
+      <c r="H76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>I1</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Xeppaa</t>
+          <t>Killua</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Cloud9</t>
+          <t>FULL SENSE</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>AMER</t>
+          <t>PAC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="F77" t="n">
-        <v>7.3</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="G77" t="n">
-        <v>7.3</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>I2</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -14811,49 +14811,49 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C1</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Dos9</t>
+          <t>v1c</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Karmine Corp</t>
+          <t>Cloud9</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>EMEA</t>
+          <t>AMER</t>
         </is>
       </c>
       <c r="E79" t="n">
         <v>8</v>
       </c>
       <c r="F79" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="G79" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>supamen</t>
+          <t>Erde</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Evil Geniuses</t>
+          <t>LOUD</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -14865,27 +14865,27 @@
         <v>6.5</v>
       </c>
       <c r="F80" t="n">
-        <v>7.2</v>
+        <v>6.9</v>
       </c>
       <c r="G80" t="n">
-        <v>7.2</v>
+        <v>6.9</v>
       </c>
       <c r="H80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Cryocells</t>
+          <t>skuba</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>100 Thieves</t>
+          <t>NRG Esports</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -14894,30 +14894,30 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>10.5</v>
+        <v>9.5</v>
       </c>
       <c r="F81" t="n">
-        <v>9.1</v>
+        <v>8.9</v>
       </c>
       <c r="G81" t="n">
-        <v>9.1</v>
+        <v>8.9</v>
       </c>
       <c r="H81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>skuba</t>
+          <t>Bao</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>NRG Esports</t>
+          <t>Evil Geniuses</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -14926,20 +14926,20 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>9.5</v>
+        <v>6.5</v>
       </c>
       <c r="F82" t="n">
-        <v>8.9</v>
+        <v>7.1</v>
       </c>
       <c r="G82" t="n">
-        <v>8.9</v>
+        <v>7.1</v>
       </c>
       <c r="H82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>W1</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -14971,7 +14971,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>W2</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -15003,17 +15003,17 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>W3</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>v1c</t>
+          <t>Cryocells</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Cloud9</t>
+          <t>100 Thieves</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -15022,13 +15022,13 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>8</v>
+        <v>10.5</v>
       </c>
       <c r="F85" t="n">
-        <v>8.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="G85" t="n">
-        <v>8.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="H85" t="inlineStr"/>
     </row>
@@ -15039,7 +15039,7 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G86" t="n">
         <v>108.4</v>
@@ -15060,7 +15060,7 @@
       </c>
       <c r="B89" s="7" t="inlineStr">
         <is>
-          <t>OUT: Patmen</t>
+          <t>OUT: Derke</t>
         </is>
       </c>
       <c r="C89" s="7" t="inlineStr">
@@ -15070,7 +15070,7 @@
       </c>
       <c r="D89" s="7" t="inlineStr">
         <is>
-          <t>Slot: D</t>
+          <t>Slot: D2</t>
         </is>
       </c>
     </row>
@@ -15082,17 +15082,17 @@
       </c>
       <c r="B90" s="7" t="inlineStr">
         <is>
-          <t>OUT: Udotan</t>
+          <t>OUT: Patmen</t>
         </is>
       </c>
       <c r="C90" s="7" t="inlineStr">
         <is>
-          <t>IN: Neon</t>
+          <t>IN: Keiko</t>
         </is>
       </c>
       <c r="D90" s="7" t="inlineStr">
         <is>
-          <t>Slot: W</t>
+          <t>Slot: W1</t>
         </is>
       </c>
     </row>
@@ -15104,7 +15104,7 @@
       </c>
       <c r="B91" s="7" t="inlineStr">
         <is>
-          <t>OUT: Derke</t>
+          <t>OUT: Udotan</t>
         </is>
       </c>
       <c r="C91" s="7" t="inlineStr">
@@ -15114,7 +15114,7 @@
       </c>
       <c r="D91" s="7" t="inlineStr">
         <is>
-          <t>Slot: W</t>
+          <t>Slot: W2</t>
         </is>
       </c>
     </row>
@@ -15163,107 +15163,107 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D1</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>BABYBAY</t>
+          <t>dgzin</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>G2 Esports</t>
+          <t>Evil Geniuses</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>EMEA</t>
+          <t>AMER</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="F93" t="n">
-        <v>8.800000000000001</v>
+        <v>10.1</v>
       </c>
       <c r="G93" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="H93" t="inlineStr"/>
+        <v>20.3</v>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>IGL</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>dgzin</t>
+          <t>BABYBAY</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Evil Geniuses</t>
+          <t>G2 Esports</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>AMER</t>
+          <t>EMEA</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="F94" t="n">
-        <v>10.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="G94" t="n">
-        <v>20.3</v>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>IGL</t>
-        </is>
-      </c>
+        <v>8.800000000000001</v>
+      </c>
+      <c r="H94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>I1</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Xeppaa</t>
+          <t>Killua</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Cloud9</t>
+          <t>FULL SENSE</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>AMER</t>
+          <t>PAC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="F95" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="G95" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="H95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>I2</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -15295,49 +15295,49 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C1</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Dos9</t>
+          <t>v1c</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Karmine Corp</t>
+          <t>Cloud9</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>EMEA</t>
+          <t>AMER</t>
         </is>
       </c>
       <c r="E97" t="n">
         <v>8</v>
       </c>
       <c r="F97" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="G97" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>supamen</t>
+          <t>Erde</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Evil Geniuses</t>
+          <t>LOUD</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -15349,27 +15349,27 @@
         <v>6.5</v>
       </c>
       <c r="F98" t="n">
-        <v>7.2</v>
+        <v>6.9</v>
       </c>
       <c r="G98" t="n">
-        <v>7.2</v>
+        <v>6.9</v>
       </c>
       <c r="H98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Cryocells</t>
+          <t>skuba</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>100 Thieves</t>
+          <t>NRG Esports</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -15378,30 +15378,30 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>10.5</v>
+        <v>9.5</v>
       </c>
       <c r="F99" t="n">
-        <v>9.1</v>
+        <v>8.9</v>
       </c>
       <c r="G99" t="n">
-        <v>9.1</v>
+        <v>8.9</v>
       </c>
       <c r="H99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>skuba</t>
+          <t>Bao</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>NRG Esports</t>
+          <t>Evil Geniuses</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -15410,30 +15410,30 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>9.5</v>
+        <v>6.5</v>
       </c>
       <c r="F100" t="n">
-        <v>8.9</v>
+        <v>7.1</v>
       </c>
       <c r="G100" t="n">
-        <v>8.9</v>
+        <v>7.1</v>
       </c>
       <c r="H100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>W1</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Neon</t>
+          <t>Keiko</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>LEVIATÁN</t>
+          <t>NRG Esports</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -15442,20 +15442,20 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="F101" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="G101" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="H101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>W2</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -15487,17 +15487,17 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>W3</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>v1c</t>
+          <t>Cryocells</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Cloud9</t>
+          <t>100 Thieves</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -15506,13 +15506,13 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>8</v>
+        <v>10.5</v>
       </c>
       <c r="F103" t="n">
-        <v>8.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="G103" t="n">
-        <v>8.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="H103" t="inlineStr"/>
     </row>
@@ -15526,7 +15526,7 @@
         <v>100</v>
       </c>
       <c r="G104" t="n">
-        <v>93.90000000000001</v>
+        <v>94</v>
       </c>
     </row>
   </sheetData>
@@ -25630,17 +25630,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Primmie</t>
+          <t>Derke</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>FULL SENSE</t>
+          <t>Team Vitality</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>PAC</t>
+          <t>EMEA</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -25649,36 +25649,36 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>12</v>
+        <v>10.6</v>
       </c>
       <c r="F2" t="n">
-        <v>13.4</v>
+        <v>12.4</v>
       </c>
       <c r="G2" t="n">
-        <v>11.1</v>
+        <v>11.2</v>
       </c>
       <c r="H2" t="n">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>47.5</v>
+        <v>47.7</v>
       </c>
       <c r="L2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>HYUNMIN</t>
+          <t>Primmie</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>DRX</t>
+          <t>FULL SENSE</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -25692,41 +25692,41 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>10.3</v>
+        <v>12</v>
       </c>
       <c r="F3" t="n">
-        <v>11.8</v>
+        <v>13.4</v>
       </c>
       <c r="G3" t="n">
-        <v>10.3</v>
+        <v>11.1</v>
       </c>
       <c r="H3" t="n">
-        <v>10.2</v>
+        <v>11</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>42.6</v>
+        <v>47.5</v>
       </c>
       <c r="L3" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Derke</t>
+          <t>HYUNMIN</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Team Vitality</t>
+          <t>DRX</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>EMEA</t>
+          <t>PAC</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -25738,22 +25738,22 @@
         <v>10.3</v>
       </c>
       <c r="F4" t="n">
-        <v>12.1</v>
+        <v>11.8</v>
       </c>
       <c r="G4" t="n">
-        <v>10.8</v>
+        <v>10.3</v>
       </c>
       <c r="H4" t="n">
-        <v>13.1</v>
+        <v>10.2</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>46.3</v>
+        <v>42.6</v>
       </c>
       <c r="L4" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5">
@@ -26126,25 +26126,25 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>9.9</v>
+        <v>10.1</v>
       </c>
       <c r="F13" t="n">
-        <v>12</v>
+        <v>12.2</v>
       </c>
       <c r="G13" t="n">
-        <v>10.4</v>
+        <v>10.7</v>
       </c>
       <c r="H13" t="n">
-        <v>9.9</v>
+        <v>10.1</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>42.2</v>
+        <v>43.1</v>
       </c>
       <c r="L13" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14">
@@ -26369,62 +26369,60 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Zekken</t>
+          <t>Kaajak</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>MIBR</t>
+          <t>FNATIC</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>AMER</t>
+          <t>EMEA</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="F19" t="n">
-        <v>10.2</v>
+        <v>11.6</v>
       </c>
       <c r="G19" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="H19" t="n">
         <v>9.6</v>
       </c>
-      <c r="H19" t="n">
-        <v>9.5</v>
-      </c>
       <c r="I19" t="n">
-        <v>10.6</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>48.8</v>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>40.8</v>
+      </c>
+      <c r="L19" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Ruxic</t>
+          <t>Zekken</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Natus Vincere</t>
+          <t>MIBR</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>EMEA</t>
+          <t>AMER</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -26433,36 +26431,38 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>9.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="F20" t="n">
-        <v>10.1</v>
+        <v>10.2</v>
       </c>
       <c r="G20" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="H20" t="n">
-        <v>9.800000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>10.6</v>
       </c>
       <c r="K20" t="n">
-        <v>38.7</v>
-      </c>
-      <c r="L20" t="n">
-        <v>15</v>
+        <v>48.8</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Kaajak</t>
+          <t>Ruxic</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>FNATIC</t>
+          <t>Natus Vincere</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -26472,85 +26472,83 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>9.300000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="F21" t="n">
-        <v>11.3</v>
+        <v>10.1</v>
       </c>
       <c r="G21" t="n">
-        <v>9.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="H21" t="n">
-        <v>9.300000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>39.8</v>
+        <v>38.7</v>
       </c>
       <c r="L21" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>skuba</t>
+          <t>Veqaj</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>NRG Esports</t>
+          <t>FNATIC</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>AMER</t>
+          <t>EMEA</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>10.4</v>
+        <v>9.4</v>
       </c>
       <c r="F22" t="n">
-        <v>9.699999999999999</v>
+        <v>11.3</v>
       </c>
       <c r="G22" t="n">
-        <v>9.300000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="H22" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="I22" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>48</v>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>39.9</v>
+      </c>
+      <c r="L22" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Veqaj</t>
+          <t>Sayonara</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>FNATIC</t>
+          <t>Team Vitality</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -26560,69 +26558,69 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>I</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>9.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>11</v>
+        <v>10.3</v>
       </c>
       <c r="G23" t="n">
-        <v>9.699999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="H23" t="n">
-        <v>9.1</v>
+        <v>11.2</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>39</v>
+        <v>39.5</v>
       </c>
       <c r="L23" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>jawgemo</t>
+          <t>skuba</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>G2 Esports</t>
+          <t>NRG Esports</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>EMEA</t>
+          <t>AMER</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>9.4</v>
+        <v>10.4</v>
       </c>
       <c r="F24" t="n">
-        <v>9.1</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="G24" t="n">
-        <v>9.800000000000001</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="H24" t="n">
-        <v>10.1</v>
+        <v>9.6</v>
       </c>
       <c r="I24" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="K24" t="n">
-        <v>47.5</v>
+        <v>48</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -26633,17 +26631,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>dgzin</t>
+          <t>jawgemo</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Evil Geniuses</t>
+          <t>G2 Esports</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>AMER</t>
+          <t>EMEA</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -26652,22 +26650,22 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="F25" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="G25" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="H25" t="n">
         <v>10.1</v>
       </c>
-      <c r="G25" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="H25" t="n">
-        <v>8.699999999999999</v>
-      </c>
       <c r="I25" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="K25" t="n">
-        <v>45.8</v>
+        <v>47.5</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -26678,44 +26676,46 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Sayonara</t>
+          <t>dgzin</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Team Vitality</t>
+          <t>Evil Geniuses</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>EMEA</t>
+          <t>AMER</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="F26" t="n">
-        <v>9.9</v>
+        <v>10.1</v>
       </c>
       <c r="G26" t="n">
-        <v>8.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="H26" t="n">
-        <v>10.8</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="K26" t="n">
-        <v>38.1</v>
-      </c>
-      <c r="L26" t="n">
-        <v>12</v>
+        <v>45.8</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="27">
@@ -27419,12 +27419,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>BABYBAY</t>
+          <t>Chronicle</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>G2 Esports</t>
+          <t>Team Vitality</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -27434,80 +27434,80 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>8.6</v>
+        <v>7.9</v>
       </c>
       <c r="F43" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="G43" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="G43" t="n">
-        <v>9</v>
-      </c>
       <c r="H43" t="n">
-        <v>9.300000000000001</v>
+        <v>10.1</v>
       </c>
       <c r="I43" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>43.6</v>
-      </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>35.5</v>
+      </c>
+      <c r="L43" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>invy</t>
+          <t>BABYBAY</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Paper Rex</t>
+          <t>G2 Esports</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>PAC</t>
+          <t>EMEA</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="F44" t="n">
-        <v>8.800000000000001</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="G44" t="n">
         <v>9</v>
       </c>
       <c r="H44" t="n">
-        <v>8</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I44" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="K44" t="n">
-        <v>33.6</v>
-      </c>
-      <c r="L44" t="n">
-        <v>10</v>
+        <v>43.6</v>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>d4v41</t>
+          <t>invy</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -27522,63 +27522,63 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>I</t>
         </is>
       </c>
       <c r="E45" t="n">
         <v>7.8</v>
       </c>
       <c r="F45" t="n">
-        <v>8.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="G45" t="n">
         <v>9</v>
       </c>
       <c r="H45" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="I45" t="n">
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>33.5</v>
+        <v>33.6</v>
       </c>
       <c r="L45" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>kamo</t>
+          <t>d4v41</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Team Liquid</t>
+          <t>Paper Rex</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>EMEA</t>
+          <t>PAC</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E46" t="n">
         <v>7.8</v>
       </c>
       <c r="F46" t="n">
-        <v>8.4</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="G46" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="H46" t="n">
-        <v>8.800000000000001</v>
+        <v>7.9</v>
       </c>
       <c r="I46" t="n">
         <v>0</v>
@@ -27593,186 +27593,184 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>xavi8k</t>
+          <t>kamo</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Global Esports</t>
+          <t>Team Liquid</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>PAC</t>
+          <t>EMEA</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="F47" t="n">
-        <v>7.9</v>
+        <v>8.4</v>
       </c>
       <c r="G47" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="H47" t="n">
-        <v>7.7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I47" t="n">
         <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>31.8</v>
+        <v>33.5</v>
       </c>
       <c r="L47" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Keznit</t>
+          <t>PROFEK</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>ENVY</t>
+          <t>Team Vitality</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>AMER</t>
+          <t>EMEA</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>8.800000000000001</v>
+        <v>7.7</v>
       </c>
       <c r="F48" t="n">
-        <v>8.300000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="G48" t="n">
         <v>8.1</v>
       </c>
       <c r="H48" t="n">
-        <v>7.6</v>
+        <v>9.9</v>
       </c>
       <c r="I48" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>41.2</v>
-      </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>34.7</v>
+      </c>
+      <c r="L48" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Francis</t>
+          <t>Crashies</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Nongshim RedForce</t>
+          <t>FNATIC</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>PAC</t>
+          <t>EMEA</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>I</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="F49" t="n">
-        <v>7.7</v>
+        <v>9.9</v>
       </c>
       <c r="G49" t="n">
         <v>8.6</v>
       </c>
       <c r="H49" t="n">
-        <v>8.800000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="I49" t="n">
         <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>33</v>
+        <v>34.8</v>
       </c>
       <c r="L49" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Miniboo</t>
+          <t>xavi8k</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Team Liquid</t>
+          <t>Global Esports</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>EMEA</t>
+          <t>PAC</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="F50" t="n">
-        <v>8.300000000000001</v>
+        <v>7.9</v>
       </c>
       <c r="G50" t="n">
-        <v>8.300000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="H50" t="n">
-        <v>8.699999999999999</v>
+        <v>7.7</v>
       </c>
       <c r="I50" t="n">
         <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>33.2</v>
+        <v>31.8</v>
       </c>
       <c r="L50" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Neon</t>
+          <t>Keznit</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>LEVIATÁN</t>
+          <t>ENVY</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -27786,22 +27784,22 @@
         </is>
       </c>
       <c r="E51" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="F51" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="G51" t="n">
         <v>8.1</v>
       </c>
-      <c r="F51" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="G51" t="n">
-        <v>8.9</v>
-      </c>
       <c r="H51" t="n">
-        <v>8.300000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="I51" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="K51" t="n">
-        <v>41.4</v>
+        <v>41.2</v>
       </c>
       <c r="L51" t="inlineStr">
         <is>
@@ -27812,41 +27810,41 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Chronicle</t>
+          <t>Francis</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Team Vitality</t>
+          <t>Nongshim RedForce</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>EMEA</t>
+          <t>PAC</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>7.5</v>
+        <v>7.8</v>
       </c>
       <c r="F52" t="n">
-        <v>8.9</v>
+        <v>7.7</v>
       </c>
       <c r="G52" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="H52" t="n">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I52" t="n">
         <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L52" t="n">
         <v>6</v>
@@ -27855,57 +27853,55 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>ethan</t>
+          <t>Miniboo</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>NRG Esports</t>
+          <t>Team Liquid</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>AMER</t>
+          <t>EMEA</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>8.9</v>
+        <v>7.8</v>
       </c>
       <c r="F53" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="G53" t="n">
-        <v>8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="H53" t="n">
-        <v>8.199999999999999</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I53" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>41.2</v>
-      </c>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>33.2</v>
+      </c>
+      <c r="L53" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>JohnQT</t>
+          <t>Neon</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Sentinels</t>
+          <t>LEVIATÁN</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -27915,26 +27911,26 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E54" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="F54" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="G54" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="H54" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="F54" t="n">
-        <v>8</v>
-      </c>
-      <c r="G54" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="H54" t="n">
-        <v>8.9</v>
-      </c>
       <c r="I54" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="K54" t="n">
-        <v>41</v>
+        <v>41.4</v>
       </c>
       <c r="L54" t="inlineStr">
         <is>
@@ -27945,7 +27941,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>brawk</t>
+          <t>ethan</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -27979,7 +27975,7 @@
         <v>7.7</v>
       </c>
       <c r="K55" t="n">
-        <v>41</v>
+        <v>41.2</v>
       </c>
       <c r="L55" t="inlineStr">
         <is>
@@ -27990,60 +27986,62 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Crashies</t>
+          <t>JohnQT</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>FNATIC</t>
+          <t>Sentinels</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>EMEA</t>
+          <t>AMER</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>7.9</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="F56" t="n">
-        <v>9.6</v>
+        <v>8</v>
       </c>
       <c r="G56" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H56" t="n">
-        <v>7.9</v>
+        <v>8.9</v>
       </c>
       <c r="I56" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="K56" t="n">
-        <v>33.8</v>
-      </c>
-      <c r="L56" t="n">
-        <v>10</v>
+        <v>41</v>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Rosé</t>
+          <t>brawk</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>BBL Esports</t>
+          <t>NRG Esports</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>EMEA</t>
+          <t>AMER</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -28052,86 +28050,86 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="F57" t="n">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="G57" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="H57" t="n">
-        <v>7.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I57" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="K57" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="L57" t="n">
-        <v>9</v>
+        <v>41</v>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>v1c</t>
+          <t>Rosé</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Cloud9</t>
+          <t>BBL Esports</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>AMER</t>
+          <t>EMEA</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>I</t>
         </is>
       </c>
       <c r="E58" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="F58" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="G58" t="n">
         <v>7.9</v>
       </c>
-      <c r="F58" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="G58" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="H58" t="n">
-        <v>8.6</v>
+        <v>7.5</v>
       </c>
       <c r="I58" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>40.9</v>
-      </c>
-      <c r="L58" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>32.5</v>
+      </c>
+      <c r="L58" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Loita</t>
+          <t>v1c</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>BBL Esports</t>
+          <t>Cloud9</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>EMEA</t>
+          <t>AMER</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -28140,36 +28138,38 @@
         </is>
       </c>
       <c r="E59" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="F59" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="F59" t="n">
-        <v>8.300000000000001</v>
-      </c>
       <c r="G59" t="n">
-        <v>7.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H59" t="n">
-        <v>7.5</v>
+        <v>8.6</v>
       </c>
       <c r="I59" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="K59" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="L59" t="n">
-        <v>6</v>
+        <v>40.9</v>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>bipo</t>
+          <t>Loita</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Gentle Mates</t>
+          <t>BBL Esports</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -28179,40 +28179,40 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="F60" t="n">
-        <v>8.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="G60" t="n">
-        <v>7.6</v>
+        <v>7.9</v>
       </c>
       <c r="H60" t="n">
-        <v>7.8</v>
+        <v>7.5</v>
       </c>
       <c r="I60" t="n">
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>31.6</v>
+        <v>32.5</v>
       </c>
       <c r="L60" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>valyn</t>
+          <t>bipo</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>G2 Esports</t>
+          <t>Gentle Mates</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -28222,71 +28222,69 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E61" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="F61" t="n">
-        <v>7.9</v>
+        <v>8.1</v>
       </c>
       <c r="G61" t="n">
-        <v>8.5</v>
+        <v>7.6</v>
       </c>
       <c r="H61" t="n">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="I61" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>41.5</v>
-      </c>
-      <c r="L61" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>31.6</v>
+      </c>
+      <c r="L61" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Lukxo</t>
+          <t>valyn</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>LOUD</t>
+          <t>G2 Esports</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>AMER</t>
+          <t>EMEA</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E62" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="F62" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="G62" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H62" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="F62" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="G62" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="H62" t="n">
+      <c r="I62" t="n">
         <v>8</v>
       </c>
-      <c r="I62" t="n">
-        <v>7.9</v>
-      </c>
       <c r="K62" t="n">
-        <v>40.1</v>
+        <v>41.5</v>
       </c>
       <c r="L62" t="inlineStr">
         <is>
@@ -28297,12 +28295,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>eeiu</t>
+          <t>Lukxo</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>FURIA</t>
+          <t>LOUD</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -28312,26 +28310,26 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>7.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="F63" t="n">
         <v>8.1</v>
       </c>
       <c r="G63" t="n">
-        <v>8.199999999999999</v>
+        <v>7.3</v>
       </c>
       <c r="H63" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="I63" t="n">
         <v>7.9</v>
       </c>
       <c r="K63" t="n">
-        <v>39.3</v>
+        <v>40.1</v>
       </c>
       <c r="L63" t="inlineStr">
         <is>
@@ -28342,17 +28340,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>seven</t>
+          <t>eeiu</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>PCIFIC Esports</t>
+          <t>FURIA</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>EMEA</t>
+          <t>AMER</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -28361,31 +28359,33 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>8.300000000000001</v>
+        <v>7.5</v>
       </c>
       <c r="F64" t="n">
-        <v>7.4</v>
+        <v>8.1</v>
       </c>
       <c r="G64" t="n">
-        <v>8.699999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H64" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="I64" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="K64" t="n">
-        <v>32.2</v>
-      </c>
-      <c r="L64" t="n">
-        <v>6</v>
+        <v>39.3</v>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>PROFEK</t>
+          <t>Jamppi</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -28400,7 +28400,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>I</t>
         </is>
       </c>
       <c r="E65" t="n">
@@ -28413,101 +28413,99 @@
         <v>7.8</v>
       </c>
       <c r="H65" t="n">
-        <v>9.4</v>
+        <v>9.5</v>
       </c>
       <c r="I65" t="n">
         <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>33.3</v>
+        <v>33.4</v>
       </c>
       <c r="L65" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Timotino</t>
+          <t>seven</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>100 Thieves</t>
+          <t>PCIFIC Esports</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>AMER</t>
+          <t>EMEA</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>I</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>8.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="F66" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="G66" t="n">
-        <v>7.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="H66" t="n">
-        <v>8.1</v>
+        <v>7.8</v>
       </c>
       <c r="I66" t="n">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>40</v>
-      </c>
-      <c r="L66" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>32.2</v>
+      </c>
+      <c r="L66" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>trent</t>
+          <t>Timotino</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>G2 Esports</t>
+          <t>100 Thieves</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>EMEA</t>
+          <t>AMER</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E67" t="n">
         <v>8.1</v>
       </c>
       <c r="F67" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="G67" t="n">
-        <v>8.4</v>
+        <v>7.5</v>
       </c>
       <c r="H67" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="I67" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="I67" t="n">
-        <v>7.9</v>
-      </c>
       <c r="K67" t="n">
-        <v>40.9</v>
+        <v>40</v>
       </c>
       <c r="L67" t="inlineStr">
         <is>
@@ -28518,41 +28516,41 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Demon1</t>
+          <t>trent</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>ENVY</t>
+          <t>G2 Esports</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>AMER</t>
+          <t>EMEA</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>I</t>
         </is>
       </c>
       <c r="E68" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="F68" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="G68" t="n">
         <v>8.4</v>
       </c>
-      <c r="F68" t="n">
+      <c r="H68" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="I68" t="n">
         <v>7.9</v>
       </c>
-      <c r="G68" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="H68" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="I68" t="n">
-        <v>8.1</v>
-      </c>
       <c r="K68" t="n">
-        <v>39.5</v>
+        <v>40.9</v>
       </c>
       <c r="L68" t="inlineStr">
         <is>
@@ -28563,55 +28561,57 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>LewN</t>
+          <t>Demon1</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Karmine Corp</t>
+          <t>ENVY</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>EMEA</t>
+          <t>AMER</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="F69" t="n">
-        <v>7.4</v>
+        <v>7.9</v>
       </c>
       <c r="G69" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="H69" t="n">
-        <v>7.9</v>
+        <v>7.3</v>
       </c>
       <c r="I69" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="K69" t="n">
-        <v>31.6</v>
-      </c>
-      <c r="L69" t="n">
-        <v>4</v>
+        <v>39.5</v>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Minny</t>
+          <t>LewN</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Gentle Mates</t>
+          <t>Karmine Corp</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -28621,40 +28621,40 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E70" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="F70" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="G70" t="n">
         <v>8</v>
       </c>
-      <c r="F70" t="n">
+      <c r="H70" t="n">
         <v>7.9</v>
       </c>
-      <c r="G70" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="H70" t="n">
-        <v>7.6</v>
-      </c>
       <c r="I70" t="n">
         <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>31</v>
+        <v>31.6</v>
       </c>
       <c r="L70" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>nAts</t>
+          <t>Minny</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Team Liquid</t>
+          <t>Gentle Mates</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -28668,108 +28668,108 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>7.3</v>
+        <v>8</v>
       </c>
       <c r="F71" t="n">
         <v>7.9</v>
       </c>
       <c r="G71" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="H71" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="I71" t="n">
         <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>31.2</v>
+        <v>31</v>
       </c>
       <c r="L71" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>BeYN</t>
+          <t>nAts</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>DRX</t>
+          <t>Team Liquid</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>PAC</t>
+          <t>EMEA</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="F72" t="n">
-        <v>8.300000000000001</v>
+        <v>7.9</v>
       </c>
       <c r="G72" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="H72" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I72" t="n">
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>29.9</v>
+        <v>31.2</v>
       </c>
       <c r="L72" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Dos9</t>
+          <t>BeYN</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Karmine Corp</t>
+          <t>DRX</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>EMEA</t>
+          <t>PAC</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>I</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>8.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="F73" t="n">
-        <v>7.3</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="G73" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="H73" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="I73" t="n">
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>31.1</v>
+        <v>29.9</v>
       </c>
       <c r="L73" t="n">
         <v>8</v>
@@ -28778,67 +28778,65 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Verno</t>
+          <t>Dos9</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>MIBR</t>
+          <t>Karmine Corp</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>AMER</t>
+          <t>EMEA</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>7.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="F74" t="n">
-        <v>8.199999999999999</v>
+        <v>7.3</v>
       </c>
       <c r="G74" t="n">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="H74" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="I74" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>39</v>
-      </c>
-      <c r="L74" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>31.1</v>
+      </c>
+      <c r="L74" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>MaKo</t>
+          <t>Verno</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>DRX</t>
+          <t>MIBR</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>PAC</t>
+          <t>AMER</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>I</t>
         </is>
       </c>
       <c r="E75" t="n">
@@ -28848,35 +28846,37 @@
         <v>8.199999999999999</v>
       </c>
       <c r="G75" t="n">
-        <v>7.1</v>
+        <v>7.7</v>
       </c>
       <c r="H75" t="n">
-        <v>7.1</v>
+        <v>7.6</v>
       </c>
       <c r="I75" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="K75" t="n">
-        <v>29.5</v>
-      </c>
-      <c r="L75" t="n">
-        <v>6</v>
+        <v>39</v>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Mazino</t>
+          <t>MaKo</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>MIBR</t>
+          <t>DRX</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>AMER</t>
+          <t>PAC</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -28885,113 +28885,113 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="F76" t="n">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="G76" t="n">
-        <v>7.6</v>
+        <v>7.1</v>
       </c>
       <c r="H76" t="n">
-        <v>7.5</v>
+        <v>7.1</v>
       </c>
       <c r="I76" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>38.7</v>
-      </c>
-      <c r="L76" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>29.5</v>
+      </c>
+      <c r="L76" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>t3xture</t>
+          <t>Mazino</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Gen.G</t>
+          <t>MIBR</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>PAC</t>
+          <t>AMER</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E77" t="n">
         <v>7</v>
       </c>
       <c r="F77" t="n">
-        <v>7.1</v>
+        <v>8.1</v>
       </c>
       <c r="G77" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="H77" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="I77" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="K77" t="n">
-        <v>29.4</v>
-      </c>
-      <c r="L77" t="n">
-        <v>3</v>
+        <v>38.7</v>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Jamppi</t>
+          <t>t3xture</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Team Vitality</t>
+          <t>Gen.G</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>EMEA</t>
+          <t>PAC</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E78" t="n">
+        <v>7</v>
+      </c>
+      <c r="F78" t="n">
         <v>7.1</v>
       </c>
-      <c r="F78" t="n">
-        <v>8.300000000000001</v>
-      </c>
       <c r="G78" t="n">
-        <v>7.5</v>
+        <v>7.2</v>
       </c>
       <c r="H78" t="n">
-        <v>9.1</v>
+        <v>8</v>
       </c>
       <c r="I78" t="n">
         <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>31.9</v>
+        <v>29.4</v>
       </c>
       <c r="L78" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="79">
@@ -31895,100 +31895,98 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>ZynX</t>
+          <t>Boaster</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Gen.G</t>
+          <t>FNATIC</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>PAC</t>
+          <t>EMEA</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="F145" t="n">
-        <v>5.2</v>
+        <v>6.8</v>
       </c>
       <c r="G145" t="n">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="H145" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="I145" t="n">
         <v>0</v>
       </c>
       <c r="K145" t="n">
-        <v>21.5</v>
+        <v>23.9</v>
       </c>
       <c r="L145" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>silentzz</t>
+          <t>ZynX</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>KRÜ Esports</t>
+          <t>Gen.G</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>AMER</t>
+          <t>PAC</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E146" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="F146" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="G146" t="n">
         <v>5.3</v>
       </c>
-      <c r="F146" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="G146" t="n">
-        <v>6.1</v>
-      </c>
       <c r="H146" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="I146" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="K146" t="n">
-        <v>27.8</v>
-      </c>
-      <c r="L146" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>21.5</v>
+      </c>
+      <c r="L146" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Reduxx</t>
+          <t>silentzz</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Sentinels</t>
+          <t>KRÜ Esports</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -31998,26 +31996,26 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E147" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="F147" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="G147" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="H147" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="I147" t="n">
         <v>5.7</v>
       </c>
-      <c r="F147" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="G147" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="H147" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="I147" t="n">
-        <v>5.2</v>
-      </c>
       <c r="K147" t="n">
-        <v>28.2</v>
+        <v>27.8</v>
       </c>
       <c r="L147" t="inlineStr">
         <is>
@@ -32028,17 +32026,17 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Absol</t>
+          <t>Reduxx</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>ZETA DIVISION</t>
+          <t>Sentinels</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>PAC</t>
+          <t>AMER</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -32050,33 +32048,35 @@
         <v>5.7</v>
       </c>
       <c r="F148" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="G148" t="n">
         <v>5.7</v>
       </c>
-      <c r="G148" t="n">
-        <v>5.4</v>
-      </c>
       <c r="H148" t="n">
-        <v>6.5</v>
+        <v>6.1</v>
       </c>
       <c r="I148" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="K148" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="L148" t="n">
-        <v>10</v>
+        <v>28.2</v>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Akame</t>
+          <t>Absol</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Detonation FocusMe</t>
+          <t>ZETA DIVISION</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -32086,60 +32086,60 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E149" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="F149" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="G149" t="n">
         <v>5.4</v>
       </c>
-      <c r="F149" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="G149" t="n">
+      <c r="H149" t="n">
         <v>6.5</v>
       </c>
-      <c r="H149" t="n">
-        <v>5.4</v>
-      </c>
       <c r="I149" t="n">
         <v>0</v>
       </c>
       <c r="K149" t="n">
-        <v>23.2</v>
+        <v>23.3</v>
       </c>
       <c r="L149" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Boaster</t>
+          <t>Akame</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>FNATIC</t>
+          <t>Detonation FocusMe</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>EMEA</t>
+          <t>PAC</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>I</t>
         </is>
       </c>
       <c r="E150" t="n">
         <v>5.4</v>
       </c>
       <c r="F150" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="G150" t="n">
         <v>6.5</v>
-      </c>
-      <c r="G150" t="n">
-        <v>5.7</v>
       </c>
       <c r="H150" t="n">
         <v>5.4</v>
@@ -32148,10 +32148,10 @@
         <v>0</v>
       </c>
       <c r="K150" t="n">
-        <v>22.9</v>
+        <v>23.2</v>
       </c>
       <c r="L150" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="151">
